--- a/src/attributions/attributions_saliency_traj_59.xlsx
+++ b/src/attributions/attributions_saliency_traj_59.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG15"/>
+  <dimension ref="A1:GG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03234769403934479</v>
+        <v>4.584367885307472e-10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1150618046522141</v>
+        <v>6.781630812469075e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03090111538767815</v>
+        <v>1.104750957381384e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01023186091333628</v>
+        <v>9.282862256654312e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0460476391017437</v>
+        <v>1.012516293030785e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04793227836489677</v>
+        <v>2.739981352917198e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05075744539499283</v>
+        <v>1.600511723154341e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1257212609052658</v>
+        <v>3.976144136164095e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>0.219210758805275</v>
+        <v>1.430129348278797e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006240867078304291</v>
+        <v>4.366420836010576e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1140982061624527</v>
+        <v>2.829849465868506e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06178533285856247</v>
+        <v>6.422564702290856e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08738083392381668</v>
+        <v>8.516169991423794e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04157315194606781</v>
+        <v>1.835341212341746e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02229486405849457</v>
+        <v>4.268747577640397e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01328495051711798</v>
+        <v>1.666082494189425e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1146690249443054</v>
+        <v>1.384236947288287e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2058961242437363</v>
+        <v>1.706649044308506e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009658052586019039</v>
+        <v>7.378095356891379e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>0.006029650568962097</v>
+        <v>3.232569767419591e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01372205466032028</v>
+        <v>8.116080030262651e-11</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004663817584514618</v>
+        <v>1.732233023687968e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0511157438158989</v>
+        <v>2.503477425364053e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0841895267367363</v>
+        <v>2.009687694037865e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01647695153951645</v>
+        <v>6.424839549268313e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03473307937383652</v>
+        <v>8.378058802271937e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05330898985266685</v>
+        <v>5.138587333419764e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02069530636072159</v>
+        <v>5.062899544050481e-10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.005548436194658279</v>
+        <v>7.323328610198132e-10</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1539159417152405</v>
+        <v>1.26487886831228e-09</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.005357032641768456</v>
+        <v>3.039828833095726e-09</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.04310715943574905</v>
+        <v>1.739250632404321e-09</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.005434801336377859</v>
+        <v>8.067270462763787e-11</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.04127698019146919</v>
+        <v>5.471112451971294e-11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.04153839498758316</v>
+        <v>1.065000532207705e-09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03925694525241852</v>
+        <v>4.73117600652273e-10</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0216093435883522</v>
+        <v>7.87723497541748e-10</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01451149117201567</v>
+        <v>3.571722362316621e-10</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.04577391967177391</v>
+        <v>4.28331148327743e-10</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.01804901100695133</v>
+        <v>9.606793138772218e-10</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.04705127701163292</v>
+        <v>7.411397051626523e-10</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.02752314880490303</v>
+        <v>6.748863690120288e-10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.006119133438915014</v>
+        <v>9.607690198976115e-10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02199441567063332</v>
+        <v>6.820824460795905e-11</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.02265520766377449</v>
+        <v>2.782272190415824e-10</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01140064187347889</v>
+        <v>3.657225078335102e-10</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1651325970888138</v>
+        <v>5.102402500511971e-09</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.01067808270454407</v>
+        <v>3.052230690414603e-10</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.03016854450106621</v>
+        <v>1.272159044773957e-09</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1840387880802155</v>
+        <v>7.486753994534467e-10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.03225819393992424</v>
+        <v>4.828988320326744e-10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.02350967191159725</v>
+        <v>8.365170778290576e-10</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1127469092607498</v>
+        <v>1.301284635601974e-09</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.004822731018066406</v>
+        <v>2.037571777968594e-10</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.02594230324029922</v>
+        <v>2.698029577530292e-10</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.05135834962129593</v>
+        <v>2.697379652971676e-09</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.01197949051856995</v>
+        <v>5.861924279315645e-10</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.02727524749934673</v>
+        <v>1.281476147418914e-09</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.007394255604594946</v>
+        <v>1.932544568816752e-09</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.03869627416133881</v>
+        <v>2.214862293570263e-09</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.04552331939339638</v>
+        <v>8.530764983305517e-11</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.09653913974761963</v>
+        <v>1.358542611740177e-09</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2181840389966965</v>
+        <v>1.488335121813122e-09</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.04394485428929329</v>
+        <v>7.002445290282822e-10</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0182755384594202</v>
+        <v>1.297593477112002e-09</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0295450035482645</v>
+        <v>3.912858093091387e-10</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.04110223054885864</v>
+        <v>1.386227244104532e-10</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1887056827545166</v>
+        <v>8.220972236294699e-10</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.05070191621780396</v>
+        <v>1.089401235887522e-09</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.03130368143320084</v>
+        <v>2.385648123492956e-09</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.02291532419621944</v>
+        <v>2.934926468523003e-10</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.06632906943559647</v>
+        <v>5.22810461589529e-10</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.02114034444093704</v>
+        <v>7.724626494010067e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.08200616389513016</v>
+        <v>2.181992586614001e-09</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.04888800159096718</v>
+        <v>2.392801234929465e-10</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.03750691935420036</v>
+        <v>9.00549079752011e-10</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.05035533010959625</v>
+        <v>1.18034193530292e-09</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.008812082931399345</v>
+        <v>1.005560912314962e-11</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.001938797533512115</v>
+        <v>6.989577250315904e-10</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.07906307280063629</v>
+        <v>7.993343209555803e-10</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0689990296959877</v>
+        <v>6.781479822137726e-10</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.002017684513702989</v>
+        <v>4.551173882205717e-10</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.01887320913374424</v>
+        <v>6.425597831594132e-10</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.02880264632403851</v>
+        <v>5.306633604762467e-12</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.003402735106647015</v>
+        <v>7.719175298959158e-10</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.003078749869018793</v>
+        <v>3.172425933062328e-10</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.002243883209303021</v>
+        <v>6.45229703000183e-10</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0162755586206913</v>
+        <v>7.552919401021541e-10</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.02997301705181599</v>
+        <v>5.754448306749538e-11</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.05348504334688187</v>
+        <v>5.114417778173674e-10</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.04749935865402222</v>
+        <v>1.550552242157721e-09</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.02667834982275963</v>
+        <v>2.522977604613175e-09</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.03360321372747421</v>
+        <v>2.117649944288758e-10</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.06795153021812439</v>
+        <v>2.526559184090615e-09</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.08850228041410446</v>
+        <v>2.629886530769454e-09</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.03053700178861618</v>
+        <v>2.830258249986173e-10</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.05093143135309219</v>
+        <v>4.792916064033648e-10</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.04147633910179138</v>
+        <v>4.006548426360723e-10</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.02677569910883904</v>
+        <v>1.299642060637041e-09</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.003077112603932619</v>
+        <v>6.897984405895841e-10</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.02689389698207378</v>
+        <v>7.206625851630122e-10</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0336470827460289</v>
+        <v>6.562807242094237e-11</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0005019395612180233</v>
+        <v>5.145318615618066e-10</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.007944186218082905</v>
+        <v>1.692456938484632e-11</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.001603346318006516</v>
+        <v>6.839298571925667e-10</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.01405704580247402</v>
+        <v>3.889483735086685e-10</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.01513451524078846</v>
+        <v>1.974573421437142e-10</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.04320964217185974</v>
+        <v>6.952824982420225e-10</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.01364084705710411</v>
+        <v>4.460040392562092e-10</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.008766721934080124</v>
+        <v>4.38426517312962e-10</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01616430282592773</v>
+        <v>5.982450090868952e-10</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.007677905261516571</v>
+        <v>5.682987969102271e-10</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05777863040566444</v>
+        <v>4.972299239014433e-10</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0199402067810297</v>
+        <v>6.512688999205096e-11</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.05448788031935692</v>
+        <v>1.809563943133696e-09</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.03120070695877075</v>
+        <v>7.099788118525296e-11</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.03221186250448227</v>
+        <v>2.359623607617323e-10</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.02934273704886436</v>
+        <v>1.113935610419503e-10</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02458256855607033</v>
+        <v>3.022748717995682e-10</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.01223237998783588</v>
+        <v>6.189762036257207e-10</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.06833678483963013</v>
+        <v>2.07732608892286e-09</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.009515342302620411</v>
+        <v>1.288165574209188e-09</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.01895814761519432</v>
+        <v>1.345293987320417e-09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.01126545295119286</v>
+        <v>1.685002026796667e-09</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.01067112572491169</v>
+        <v>1.141899019785342e-09</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.1316303163766861</v>
+        <v>1.252197123768894e-09</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.03304100409150124</v>
+        <v>6.981970557262684e-10</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.048012875020504</v>
+        <v>1.333613997012151e-09</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.01561994757503271</v>
+        <v>9.913920795412423e-10</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.014242859557271</v>
+        <v>8.365064196880212e-10</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.005254700779914856</v>
+        <v>6.002041641472999e-10</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0651032030582428</v>
+        <v>8.648968208291308e-10</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.007553396746516228</v>
+        <v>6.055432821838735e-10</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.04910922795534134</v>
+        <v>8.681431129531347e-10</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.007751639932394028</v>
+        <v>4.034606537750562e-10</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.007812569849193096</v>
+        <v>1.045926345533132e-09</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.022691510617733</v>
+        <v>2.042087748899135e-10</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0614609457552433</v>
+        <v>6.298351423739135e-11</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0230773352086544</v>
+        <v>7.364772125484365e-10</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0217868760228157</v>
+        <v>2.286770356407786e-10</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01731954328715801</v>
+        <v>1.167344554353633e-10</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.05257148668169975</v>
+        <v>1.644191172101017e-10</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.04147021844983101</v>
+        <v>7.86352150061731e-10</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.04285730421543121</v>
+        <v>1.315846875904469e-10</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.04028435423970222</v>
+        <v>4.07799211066262e-10</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04308979213237762</v>
+        <v>1.241796665496508e-10</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.03489263355731964</v>
+        <v>8.876276796909721e-11</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.04065769910812378</v>
+        <v>5.919015277910944e-11</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03031162545084953</v>
+        <v>6.981477618239751e-10</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.05199985206127167</v>
+        <v>2.050609404502524e-10</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.001288164174184203</v>
+        <v>1.44532219525928e-10</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.00293682049959898</v>
+        <v>1.16836063046577e-09</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.00540089700371027</v>
+        <v>1.960471784911988e-09</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.01894845627248287</v>
+        <v>6.889549486466251e-10</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.02509980462491512</v>
+        <v>8.809376006446712e-10</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.02975553646683693</v>
+        <v>1.999147201947604e-11</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01497330795973539</v>
+        <v>5.796255697632091e-10</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.004173406399786472</v>
+        <v>1.482593908752605e-10</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.01660737954080105</v>
+        <v>3.286884653341815e-10</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.01109937764704227</v>
+        <v>3.599102682549926e-10</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.02443700656294823</v>
+        <v>1.173692670830562e-10</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05131208524107933</v>
+        <v>4.26250840179776e-10</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01463327929377556</v>
+        <v>8.528424078058094e-10</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.00192238949239254</v>
+        <v>3.528435599253754e-10</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.04341404512524605</v>
+        <v>3.416061322703001e-10</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.03794682025909424</v>
+        <v>6.038152755571957e-10</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.06894040107727051</v>
+        <v>1.353629763833908e-09</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.02381900139153004</v>
+        <v>8.921910987780279e-10</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.02574405446648598</v>
+        <v>6.876830771496145e-10</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.04730381071567535</v>
+        <v>1.317614573004278e-09</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.03078518249094486</v>
+        <v>8.193290490510208e-10</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.04927938058972359</v>
+        <v>8.624285174896329e-10</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01698473282158375</v>
+        <v>1.546996863943662e-09</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.04190836474299431</v>
+        <v>1.147551831337523e-09</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01682563871145248</v>
+        <v>5.822958226708863e-10</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.08639441430568695</v>
+        <v>5.400456193349612e-10</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.06451649218797684</v>
+        <v>1.423115292276123e-09</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.03615317493677139</v>
+        <v>6.170097766045046e-10</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.03216908872127533</v>
+        <v>6.02812466610203e-10</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.04386293143033981</v>
+        <v>6.319840206714389e-10</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0492652952671051</v>
+        <v>5.869343899789214e-10</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.001225163228809834</v>
+        <v>3.7287409271336e-10</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.004172502551227808</v>
+        <v>2.953716160547515e-10</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.04614778980612755</v>
+        <v>3.530831738096651e-10</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.001412590965628624</v>
+        <v>5.686610037025641e-13</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.03017360344529152</v>
+        <v>9.551240909289049e-10</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0243712030351162</v>
+        <v>8.458125866361854e-10</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.05262898653745651</v>
+        <v>4.22982454617582e-10</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.00280593940988183</v>
+        <v>3.305621332216901e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1144227683544159</v>
+        <v>2.400301069016564e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4225687980651855</v>
+        <v>1.361825652246296e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0953732505440712</v>
+        <v>4.135751185962988e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1869114935398102</v>
+        <v>5.665484748007543e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3226175010204315</v>
+        <v>5.421114668280325e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06710508465766907</v>
+        <v>2.002037424730929e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5204530358314514</v>
+        <v>2.809798393954566e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06849213689565659</v>
+        <v>3.690413974410944e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0399615690112114</v>
+        <v>9.946237167213212e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1502423882484436</v>
+        <v>2.822944988878362e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4158843159675598</v>
+        <v>7.561555270818587e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05440296605229378</v>
+        <v>4.997162128539401e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>0.135951042175293</v>
+        <v>2.30401531187141e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3154740333557129</v>
+        <v>1.032129492983813e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03938503935933113</v>
+        <v>1.573024266399159e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4341404139995575</v>
+        <v>5.324016338903448e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1156903579831123</v>
+        <v>2.307137592083564e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04261226579546928</v>
+        <v>1.896165224835045e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06397975981235504</v>
+        <v>1.881032440920194e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2200334221124649</v>
+        <v>9.015495017195008e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08844708651304245</v>
+        <v>1.484452560873706e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2088049203157425</v>
+        <v>1.058763965389176e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3962130844593048</v>
+        <v>7.08531400217538e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09756854921579361</v>
+        <v>4.285062860098776e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05852379649877548</v>
+        <v>1.087481105166432e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05661186203360558</v>
+        <v>6.766273652480947e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03904581442475319</v>
+        <v>2.099570295399644e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.101762942969799</v>
+        <v>5.52031975686873e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1457868367433548</v>
+        <v>3.806598591893362e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2305077612400055</v>
+        <v>2.134902032935315e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1729353368282318</v>
+        <v>7.986886707556096e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0731593444943428</v>
+        <v>1.865543275414439e-09</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.08713421225547791</v>
+        <v>1.132935856240636e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.04140065982937813</v>
+        <v>8.489016156687512e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.07134627550840378</v>
+        <v>2.713985702840205e-09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.06290221959352493</v>
+        <v>9.778440279717415e-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1616107225418091</v>
+        <v>6.62223331726608e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04494455084204674</v>
+        <v>4.789615370981437e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.07168272137641907</v>
+        <v>3.106344070857858e-10</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.02864507958292961</v>
+        <v>2.114719732659864e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02204634249210358</v>
+        <v>2.137333421359244e-09</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.04439440369606018</v>
+        <v>9.150169510974138e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08392460644245148</v>
+        <v>2.338194748929823e-09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1295633912086487</v>
+        <v>1.073256372663423e-09</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.01380365248769522</v>
+        <v>1.025114437780417e-09</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1643103510141373</v>
+        <v>4.490208760365988e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4186199903488159</v>
+        <v>1.468396959580787e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.04146052896976471</v>
+        <v>1.787664904995268e-09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.3480779230594635</v>
+        <v>1.658824411165938e-09</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1895846724510193</v>
+        <v>3.592530939400262e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.03264258801937103</v>
+        <v>1.442053143563271e-09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3781872987747192</v>
+        <v>3.8832942417244e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.05775277316570282</v>
+        <v>3.301230844243719e-09</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.06082655861973763</v>
+        <v>9.084830665528898e-10</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.03557403385639191</v>
+        <v>1.67999369971028e-09</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03470512852072716</v>
+        <v>2.257136144656613e-10</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.07889058440923691</v>
+        <v>2.043761271330879e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.05971942842006683</v>
+        <v>3.262956571603581e-11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.230348140001297</v>
+        <v>4.684799659315786e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.02039716765284538</v>
+        <v>1.136552407743352e-09</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.02074594609439373</v>
+        <v>4.793107022393883e-10</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01036946382373571</v>
+        <v>1.758351797498392e-11</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.05898769199848175</v>
+        <v>3.23029070159464e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.05154222995042801</v>
+        <v>8.7146700966656e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03731580078601837</v>
+        <v>2.46803555370434e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.006039109081029892</v>
+        <v>1.469864674419341e-09</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.2447594702243805</v>
+        <v>4.077056470208618e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.451189398765564</v>
+        <v>3.099143608409349e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.03418134152889252</v>
+        <v>5.36867439393518e-10</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1293052136898041</v>
+        <v>2.052066072621983e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.3267015814781189</v>
+        <v>1.533568549927367e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.008482326753437519</v>
+        <v>4.98416141692104e-10</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.02221528813242912</v>
+        <v>1.757065382079759e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1037462428212166</v>
+        <v>6.428286236648262e-10</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1514686197042465</v>
+        <v>1.478603572913073e-09</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.2133668512105942</v>
+        <v>5.0855375466341e-10</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.16219262778759</v>
+        <v>1.852305864247228e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.09051676094532013</v>
+        <v>1.468321908504322e-09</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1442680656909943</v>
+        <v>3.439065920929352e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1904817521572113</v>
+        <v>7.379355460024328e-10</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1101351082324982</v>
+        <v>6.859855045115992e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.03210769966244698</v>
+        <v>3.98789529176824e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1141738593578339</v>
+        <v>6.082957471065242e-10</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.02053693309426308</v>
+        <v>1.123486415011143e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01890684477984905</v>
+        <v>2.947915522799605e-10</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.06926847249269485</v>
+        <v>2.041711799627421e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03081541508436203</v>
+        <v>1.194477572408204e-10</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.06844491511583328</v>
+        <v>5.524248281041366e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0421907864511013</v>
+        <v>1.090214862831118e-10</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.03736691176891327</v>
+        <v>1.043523822907844e-09</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.2005370557308197</v>
+        <v>3.306153795179512e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.1359584033489227</v>
+        <v>1.265344717893413e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.04477710276842117</v>
+        <v>1.585873876663868e-09</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.3461169898509979</v>
+        <v>2.094542761454932e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.3971342146396637</v>
+        <v>2.273052635004547e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.03302221372723579</v>
+        <v>8.925529759729045e-10</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1817969083786011</v>
+        <v>6.707219779578111e-10</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1873553842306137</v>
+        <v>1.958892825726366e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.03883270546793938</v>
+        <v>2.073508031941174e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.04434151574969292</v>
+        <v>6.716491252056755e-11</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.09261841326951981</v>
+        <v>2.634402140877512e-10</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.04266561567783356</v>
+        <v>1.220872292151398e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03629755973815918</v>
+        <v>4.509360662652284e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0226980559527874</v>
+        <v>2.109573349340366e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.05049160867929459</v>
+        <v>3.683001403853581e-10</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.09833615273237228</v>
+        <v>1.497530155436522e-10</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.05353698879480362</v>
+        <v>6.186914869310556e-11</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.01368912309408188</v>
+        <v>1.245907044200578e-09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.01806208491325378</v>
+        <v>4.540315901024883e-10</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1615094691514969</v>
+        <v>5.834839833518402e-10</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.01826682686805725</v>
+        <v>4.25126422953781e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.2772592902183533</v>
+        <v>3.525372438417662e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03383913636207581</v>
+        <v>1.68307479064822e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.08528871089220047</v>
+        <v>9.480349838497659e-11</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.04380772262811661</v>
+        <v>3.689540672979774e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.1190817207098007</v>
+        <v>1.643142705232137e-10</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.1178324148058891</v>
+        <v>2.543305843705213e-10</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.100886806845665</v>
+        <v>8.275376217614649e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.1639583706855774</v>
+        <v>1.475544686435626e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.05744262039661407</v>
+        <v>2.547234367877849e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.007831243798136711</v>
+        <v>1.740855792853324e-10</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.04048936069011688</v>
+        <v>2.318508496301774e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.05055927112698555</v>
+        <v>2.154375122742636e-09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.009918028488755226</v>
+        <v>1.997705112444237e-09</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.04600677639245987</v>
+        <v>1.993441856029676e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.1112165078520775</v>
+        <v>1.438492436278693e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.01867240853607655</v>
+        <v>4.490607885543341e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1541479825973511</v>
+        <v>5.845492978551192e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.067839615046978</v>
+        <v>1.712213260063322e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.06122496351599693</v>
+        <v>2.355135197973368e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.07904656231403351</v>
+        <v>2.024083345375516e-09</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.03505343198776245</v>
+        <v>1.998647025658329e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.007481773383915424</v>
+        <v>3.509619261876651e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.07853466272354126</v>
+        <v>1.304845675953459e-10</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.1310242414474487</v>
+        <v>3.741312148974885e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.03734138235449791</v>
+        <v>9.274327972264018e-10</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.07179735600948334</v>
+        <v>3.755263655591534e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001184422522783279</v>
+        <v>9.794410837926648e-10</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.119193010032177</v>
+        <v>6.623077086764795e-12</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03998324647545815</v>
+        <v>9.397604916472346e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.07097610831260681</v>
+        <v>6.04837901985178e-10</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.183068186044693</v>
+        <v>1.05390718374565e-09</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.01565214060246944</v>
+        <v>2.771461671269293e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.04496067017316818</v>
+        <v>2.206322902154056e-09</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.1359395682811737</v>
+        <v>8.289944286588025e-10</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.004118142183870077</v>
+        <v>1.238518843038605e-09</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.04545879736542702</v>
+        <v>5.083051202170452e-10</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.05447143688797951</v>
+        <v>4.682993437477023e-10</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02308891713619232</v>
+        <v>6.664145346668704e-10</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.1945239007472992</v>
+        <v>3.662826153494336e-10</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.007244778797030449</v>
+        <v>1.592355580726235e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.05479642748832703</v>
+        <v>1.405781713259557e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.007888149470090866</v>
+        <v>1.8407966817513e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.05074800550937653</v>
+        <v>5.40880673582933e-10</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.08791249245405197</v>
+        <v>3.963930017558681e-10</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.01715662702918053</v>
+        <v>9.988491145307421e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02229564823210239</v>
+        <v>9.206390094718131e-10</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.008042236790060997</v>
+        <v>9.399808709176227e-11</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03113391995429993</v>
+        <v>2.887984573707314e-10</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.07407675683498383</v>
+        <v>5.030185157295364e-10</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.06999348104000092</v>
+        <v>3.51312728907871e-12</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.003089346224442124</v>
+        <v>1.323295695243587e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.1727394908666611</v>
+        <v>1.449244058093768e-09</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01359455659985542</v>
+        <v>3.631939859971567e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0856110155582428</v>
+        <v>2.265955756364235e-10</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0779753178358078</v>
+        <v>5.730721452934517e-11</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.1143175289034843</v>
+        <v>5.796506052924144e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.1617951095104218</v>
+        <v>2.199245507927827e-10</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.008619574829936028</v>
+        <v>4.991210778015898e-10</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.116737425327301</v>
+        <v>2.68710631523561e-09</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2227565050125122</v>
+        <v>4.285896970657177e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.06705622375011444</v>
+        <v>3.045087515474165e-10</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.1096944957971573</v>
+        <v>7.714302086014868e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.1445705741643906</v>
+        <v>1.882907163519576e-09</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1706502735614777</v>
+        <v>2.747259753022036e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2532143592834473</v>
+        <v>3.232712986189767e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.08931207656860352</v>
+        <v>4.269615327956444e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.03954167664051056</v>
+        <v>4.251621277262529e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.1113113462924957</v>
+        <v>7.606679730542965e-09</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.09885700047016144</v>
+        <v>1.375133895642477e-09</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.126819521188736</v>
+        <v>6.111964823141136e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.123213604092598</v>
+        <v>6.6003680299076e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.003621782641857862</v>
+        <v>3.267141002183394e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.175651490688324</v>
+        <v>1.983231578961409e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.04496940970420837</v>
+        <v>2.63644350795289e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.03031961061060429</v>
+        <v>9.152151814184606e-10</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1079892888665199</v>
+        <v>7.563334958327061e-10</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3859706819057465</v>
+        <v>1.356071366309664e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.05423162877559662</v>
+        <v>7.43201833408591e-10</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01982126757502556</v>
+        <v>0.03521525859832764</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1443744897842407</v>
+        <v>0.1478867828845978</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009599844925105572</v>
+        <v>0.09057629108428955</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1226573809981346</v>
+        <v>0.07121670246124268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02573018334805965</v>
+        <v>0.02510008029639721</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00924898125231266</v>
+        <v>0.07117162644863129</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002918751910328865</v>
+        <v>0.08770479261875153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02327017299830914</v>
+        <v>0.07664059847593307</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008711075410246849</v>
+        <v>0.07413309812545776</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02435577847063541</v>
+        <v>0.03333593532443047</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1134349331259727</v>
+        <v>0.1982732266187668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007178249303251505</v>
+        <v>0.0926617830991745</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1446656286716461</v>
+        <v>0.08760515600442886</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05522806569933891</v>
+        <v>0.04339511319994926</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02526594325900078</v>
+        <v>0.06038341671228409</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01315121818333864</v>
+        <v>0.02490272000432014</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01322895660996437</v>
+        <v>0.1414470672607422</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03185133263468742</v>
+        <v>0.05752824991941452</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01041238382458687</v>
+        <v>0.003419608809053898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04475142061710358</v>
+        <v>0.02792859449982643</v>
       </c>
       <c r="U7" t="n">
-        <v>0.006670625414699316</v>
+        <v>0.04206197708845139</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005781150888651609</v>
+        <v>0.004682861734181643</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03202991560101509</v>
+        <v>0.008700603619217873</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01667959988117218</v>
+        <v>0.04915989935398102</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01950562000274658</v>
+        <v>0.009647074155509472</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00601149769499898</v>
+        <v>0.02698936313390732</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01837287284433842</v>
+        <v>0.0589463971555233</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01115092821419239</v>
+        <v>0.02622612938284874</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03734748810529709</v>
+        <v>0.01168189477175474</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01439459342509508</v>
+        <v>0.02751880139112473</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.009917316026985645</v>
+        <v>0.1453147232532501</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.009415905922651291</v>
+        <v>0.03975838422775269</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.002685564570128918</v>
+        <v>0.1069079339504242</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01784078776836395</v>
+        <v>0.04147939756512642</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01374447252601385</v>
+        <v>0.01114974077790976</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.009839970618486404</v>
+        <v>0.0010630888864398</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.008349126204848289</v>
+        <v>0.01302570383995771</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01910214498639107</v>
+        <v>0.09821106493473053</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004172297194600105</v>
+        <v>0.03658979758620262</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01004919037222862</v>
+        <v>0.02621459029614925</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.005153247155249119</v>
+        <v>0.0590776763856411</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.005520304664969444</v>
+        <v>0.01831411942839622</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01286008488386869</v>
+        <v>0.008974554948508739</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01136098243296146</v>
+        <v>0.03605832159519196</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0006861059227958322</v>
+        <v>0.009807584807276726</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.02226509526371956</v>
+        <v>0.003991156816482544</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.09349093586206436</v>
+        <v>0.1302503645420074</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.01394798699766397</v>
+        <v>0.01676605828106403</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.016512805595994</v>
+        <v>0.06233666092157364</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.03653056547045708</v>
+        <v>0.05324835702776909</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.004377919249236584</v>
+        <v>0.03173740208148956</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001616047229617834</v>
+        <v>0.004986926447600126</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03083353117108345</v>
+        <v>0.06125099211931229</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005330529063940048</v>
+        <v>0.02000980451703072</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0004523214884102345</v>
+        <v>0.02453931048512459</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0124256294220686</v>
+        <v>0.08598244935274124</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.02270473539829254</v>
+        <v>0.07726810872554779</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04089584201574326</v>
+        <v>0.05921225249767303</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.07203663885593414</v>
+        <v>0.07629805058240891</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006550617981702089</v>
+        <v>0.07816691696643829</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.01434801332652569</v>
+        <v>0.02563852444291115</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.03176340833306313</v>
+        <v>0.04561754316091537</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.001282180193811655</v>
+        <v>0.1001396626234055</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.014890031889081</v>
+        <v>0.005397042259573936</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0003135101869702339</v>
+        <v>0.05789598077535629</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003654720727354288</v>
+        <v>0.01546530332416296</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01093943230807781</v>
+        <v>0.02515752427279949</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02727082744240761</v>
+        <v>0.02305657044053078</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01492124050855637</v>
+        <v>0.01536236889660358</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.01372497249394655</v>
+        <v>0.02203761786222458</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.008683761581778526</v>
+        <v>0.0258141066879034</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02411342039704323</v>
+        <v>0.008783085271716118</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.007684513926506042</v>
+        <v>0.01363954227417707</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05015083774924278</v>
+        <v>0.09247487783432007</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01371459476649761</v>
+        <v>0.009261363185942173</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.004193401895463467</v>
+        <v>0.02559918537735939</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02059528231620789</v>
+        <v>0.02344025485217571</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.01707806810736656</v>
+        <v>0.04157717153429985</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.002153527922928333</v>
+        <v>0.009437941014766693</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.007379338145256042</v>
+        <v>0.07400242239236832</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01110635977238417</v>
+        <v>0.04493096843361855</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0043480284512043</v>
+        <v>0.009995247237384319</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.02708177082240582</v>
+        <v>0.05566343292593956</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.005540653597563505</v>
+        <v>0.02133901603519917</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01198294758796692</v>
+        <v>0.02739891596138477</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002297078724950552</v>
+        <v>0.005649974569678307</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0005548924673348665</v>
+        <v>0.006460279226303101</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.008079882711172104</v>
+        <v>0.0148907694965601</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001232590526342392</v>
+        <v>0.01446093246340752</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.004577659536153078</v>
+        <v>0.006935217417776585</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.03594009578227997</v>
+        <v>0.04147180542349815</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.002607247792184353</v>
+        <v>0.01902926713228226</v>
       </c>
       <c r="CO7" t="n">
-        <v>2.321845386177301e-06</v>
+        <v>0.006832072511315346</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.04584908857941628</v>
+        <v>0.1145379096269608</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03006300330162048</v>
+        <v>0.1064253523945808</v>
       </c>
       <c r="CR7" t="n">
-        <v>5.080131813883781e-05</v>
+        <v>0.03245603293180466</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.01323915086686611</v>
+        <v>0.02470842003822327</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.02711446024477482</v>
+        <v>0.01190421264618635</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.002892807126045227</v>
+        <v>0.05309107899665833</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.003392371814697981</v>
+        <v>0.009717402048408985</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.02368498221039772</v>
+        <v>0.05723898112773895</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.006456943694502115</v>
+        <v>0.01918618753552437</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0173255167901516</v>
+        <v>0.03270607441663742</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01044830866158009</v>
+        <v>0.0004933932796120644</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.001344336429610848</v>
+        <v>0.009582238271832466</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01357739977538586</v>
+        <v>0.01205995492637157</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0005362238734960556</v>
+        <v>0.01535780727863312</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.00876430980861187</v>
+        <v>0.01430231612175703</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.009728889912366867</v>
+        <v>0.006746882572770119</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01687166653573513</v>
+        <v>0.03270852565765381</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.006876147352159023</v>
+        <v>0.08492864668369293</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01298389583826065</v>
+        <v>0.01591569930315018</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.008774840272963047</v>
+        <v>0.02012437954545021</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.01764638908207417</v>
+        <v>0.1057866811752319</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.01045833341777325</v>
+        <v>0.032150499522686</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.009925895370543003</v>
+        <v>0.07212971895933151</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01643703319132328</v>
+        <v>0.005220591090619564</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.008620481938123703</v>
+        <v>0.006282533518970013</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003027592785656452</v>
+        <v>0.01298873126506805</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.01146201323717833</v>
+        <v>0.01275836862623692</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.007886382751166821</v>
+        <v>0.01496255025267601</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01828596368432045</v>
+        <v>0.001287650782614946</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.005801795516163111</v>
+        <v>0.004664977081120014</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.003705955808982253</v>
+        <v>0.01723216101527214</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.01942535117268562</v>
+        <v>0.02344615384936333</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.005665707401931286</v>
+        <v>0.08285766094923019</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.002409361302852631</v>
+        <v>0.009117218665778637</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.01427978277206421</v>
+        <v>0.04478916525840759</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01643641479313374</v>
+        <v>0.04047003388404846</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.001121221343055367</v>
+        <v>0.008902322500944138</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.002575739054009318</v>
+        <v>0.02457038499414921</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01077465526759624</v>
+        <v>0.04899014532566071</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.004471150226891041</v>
+        <v>0.01543007325381041</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.004844806622713804</v>
+        <v>0.04057636484503746</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.02328872680664062</v>
+        <v>0.03809908777475357</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001792837865650654</v>
+        <v>0.01191029231995344</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01579789072275162</v>
+        <v>0.03535623475909233</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.004062815103679895</v>
+        <v>0.01287715509533882</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01588471792638302</v>
+        <v>0.02590931206941605</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01396248769015074</v>
+        <v>0.005714706610888243</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.004430769011378288</v>
+        <v>0.01721375063061714</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.009828680194914341</v>
+        <v>0.0006134216673672199</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.00219516665674746</v>
+        <v>0.006082115694880486</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.004116396885365248</v>
+        <v>0.0117398789152503</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001971594523638487</v>
+        <v>0.01869918406009674</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02213211730122566</v>
+        <v>0.03551095724105835</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.008451391942799091</v>
+        <v>0.01277816668152809</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01182832196354866</v>
+        <v>0.004958996549248695</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.02077618055045605</v>
+        <v>0.04942325502634048</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01165497675538063</v>
+        <v>0.0133995059877634</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.01537204626947641</v>
+        <v>0.02941659837961197</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.02104353718459606</v>
+        <v>0.01378729939460754</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.009387275204062462</v>
+        <v>0.047642532736063</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.001982456538826227</v>
+        <v>0.01018037367612123</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0258483961224556</v>
+        <v>0.06115373596549034</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0004484138626139611</v>
+        <v>0.01330907084047794</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01327631250023842</v>
+        <v>0.03142887726426125</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.006829619407653809</v>
+        <v>0.00131762120872736</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.003920582588762045</v>
+        <v>0.01306060142815113</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.009572750888764858</v>
+        <v>0.01110714767128229</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001959268935024738</v>
+        <v>0.01488062180578709</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.002572220051661134</v>
+        <v>0.01246947143226862</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.001220338046550751</v>
+        <v>0.0142388828098774</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.01413259189575911</v>
+        <v>0.02432860061526299</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02292978577315807</v>
+        <v>0.03444896265864372</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01741010695695877</v>
+        <v>0.0372546911239624</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01329129934310913</v>
+        <v>0.06095299124717712</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.009331816807389259</v>
+        <v>0.02353981137275696</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.007361264433711767</v>
+        <v>0.001299389638006687</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.004315377213060856</v>
+        <v>0.01639380306005478</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0242987684905529</v>
+        <v>0.06858557462692261</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.003938472364097834</v>
+        <v>0.0278965700417757</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01565285585820675</v>
+        <v>0.04015647619962692</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0007506210822612047</v>
+        <v>0.02490327134728432</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.012270363047719</v>
+        <v>0.0327734649181366</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001534558832645416</v>
+        <v>0.08870035409927368</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002638057805597782</v>
+        <v>0.007271394599229097</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.02477916702628136</v>
+        <v>0.03949682787060738</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.002726498991250992</v>
+        <v>0.02046621218323708</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.01901146769523621</v>
+        <v>0.03360605984926224</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0263042077422142</v>
+        <v>0.01163178402930498</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.006097458302974701</v>
+        <v>0.07906022667884827</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.002791185630485415</v>
+        <v>0.04611362889409065</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0273157674819231</v>
+        <v>0.001083770766854286</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.008145548403263092</v>
+        <v>0.005082597024738789</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.02795948274433613</v>
+        <v>0.01570805162191391</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.04002422466874123</v>
+        <v>0.05806436389684677</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.003473272081464529</v>
+        <v>0.01320815458893776</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01117567904293537</v>
+        <v>0.005714220926165581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003055310808122158</v>
+        <v>0.2121837139129639</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01478627324104309</v>
+        <v>0.6353931427001953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001528320135548711</v>
+        <v>0.1054412052035332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004033893346786499</v>
+        <v>0.03330476582050323</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002981517463922501</v>
+        <v>0.09072063118219376</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01331219263374805</v>
+        <v>0.5210776329040527</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001891077263280749</v>
+        <v>0.04058190435171127</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003505697241052985</v>
+        <v>0.04789681732654572</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006518685258924961</v>
+        <v>0.1886725276708603</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00576865766197443</v>
+        <v>0.1362975239753723</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009979585185647011</v>
+        <v>0.8774100542068481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009945462225005031</v>
+        <v>0.01242615282535553</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005184822250157595</v>
+        <v>0.1223335638642311</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004343342967331409</v>
+        <v>0.277722030878067</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0119335912168026</v>
+        <v>0.5266869068145752</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002073786687105894</v>
+        <v>0.1629849970340729</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00369932665489614</v>
+        <v>0.2334699183702469</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00199161353521049</v>
+        <v>0.2089056670665741</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001192734926007688</v>
+        <v>0.02759821526706219</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001839959062635899</v>
+        <v>0.1957692205905914</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0006581135676242411</v>
+        <v>0.07701557874679565</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002100628335028887</v>
+        <v>0.2205487489700317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001255991170182824</v>
+        <v>0.2194158732891083</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001527208951301873</v>
+        <v>0.09624681621789932</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001677485066466033</v>
+        <v>0.05101676657795906</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.371997106820345e-05</v>
+        <v>0.1174713373184204</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0003539005701895803</v>
+        <v>0.0476902574300766</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001878895331174135</v>
+        <v>0.002131820656359196</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002400076948106289</v>
+        <v>0.1570510119199753</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0007869910914450884</v>
+        <v>0.09270752966403961</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002701283432543278</v>
+        <v>0.2089922577142715</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001890053506940603</v>
+        <v>0.2997967600822449</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001937479944899678</v>
+        <v>0.07471884787082672</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008424523985013366</v>
+        <v>0.07323352992534637</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0008055687067098916</v>
+        <v>0.1987861692905426</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001214493066072464</v>
+        <v>0.02525835111737251</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0008190571679733694</v>
+        <v>0.002560585737228394</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001543064834550023</v>
+        <v>0.2780722677707672</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001378784072585404</v>
+        <v>0.04359859228134155</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0007021339843049645</v>
+        <v>0.1263338029384613</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0006960880709812045</v>
+        <v>0.08352019637823105</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.002564118709415197</v>
+        <v>0.07969570159912109</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002511768601834774</v>
+        <v>0.07551299035549164</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001162875909358263</v>
+        <v>0.2809167504310608</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00267418846487999</v>
+        <v>0.05443479120731354</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.003030399093404412</v>
+        <v>0.1026199460029602</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.00955075491219759</v>
+        <v>0.9539262652397156</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001985218841582537</v>
+        <v>0.04923125356435776</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001741069136187434</v>
+        <v>0.0001639388501644135</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001938159577548504</v>
+        <v>0.03123323991894722</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.005369098857045174</v>
+        <v>0.493005096912384</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001948634861037135</v>
+        <v>0.008487578481435776</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003621298354119062</v>
+        <v>0.05242470279335976</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003435848047956824</v>
+        <v>0.08397870510816574</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.005489691160619259</v>
+        <v>0.03556349128484726</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.00275233993306756</v>
+        <v>0.2752040028572083</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.004044299479573965</v>
+        <v>0.06616982817649841</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002641319530084729</v>
+        <v>0.08689660578966141</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.007235381286591291</v>
+        <v>0.285740464925766</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.006614161655306816</v>
+        <v>0.1431638300418854</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.000600889150518924</v>
+        <v>0.1413990408182144</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.005335873458534479</v>
+        <v>0.1365470588207245</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001856926362961531</v>
+        <v>0.1040283963084221</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001267042011022568</v>
+        <v>0.1070412322878838</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.003661262104287744</v>
+        <v>0.08188886940479279</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001190506271086633</v>
+        <v>0.02372888475656509</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003450775984674692</v>
+        <v>0.06138812005519867</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0005704576033167541</v>
+        <v>0.1076631546020508</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0004075069446116686</v>
+        <v>0.08936209976673126</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002890226896852255</v>
+        <v>0.06814351677894592</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0009680227376520634</v>
+        <v>0.04008273780345917</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001053795218467712</v>
+        <v>0.08972256630659103</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001393182668834925</v>
+        <v>0.08426476269960403</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.004029400181025267</v>
+        <v>0.6171715259552002</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.003283517900854349</v>
+        <v>0.01049918681383133</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0003951321123167872</v>
+        <v>0.2081935554742813</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001459928345866501</v>
+        <v>0.1511417031288147</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0006073174299672246</v>
+        <v>0.314567506313324</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002029782626777887</v>
+        <v>0.09992698580026627</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002878883155062795</v>
+        <v>0.03332799673080444</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001547957770526409</v>
+        <v>0.08629275858402252</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0002640188031364232</v>
+        <v>0.0348539724946022</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.002428736072033644</v>
+        <v>0.2550064027309418</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001863739918917418</v>
+        <v>0.01262848079204559</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001494146417826414</v>
+        <v>0.0389593318104744</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001267113839276135</v>
+        <v>0.044159185141325</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002270967699587345</v>
+        <v>0.1528779715299606</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0009487526840530336</v>
+        <v>0.0644204244017601</v>
       </c>
       <c r="CK8" t="n">
-        <v>8.909509051591158e-05</v>
+        <v>0.03250906243920326</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001262204954400659</v>
+        <v>0.00533680384978652</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001317795598879457</v>
+        <v>0.1925629377365112</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0001147588191088289</v>
+        <v>0.5052779316902161</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002177235670387745</v>
+        <v>0.03379792347550392</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.002089215442538261</v>
+        <v>0.3513935804367065</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0009334289934486151</v>
+        <v>0.3338551819324493</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0004349430673755705</v>
+        <v>0.3180845975875854</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00037814537063241</v>
+        <v>0.04802383482456207</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0002606179914437234</v>
+        <v>0.08739332109689713</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001471759169362485</v>
+        <v>0.0976848229765892</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0006345635047182441</v>
+        <v>0.005165815353393555</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.002268869429826736</v>
+        <v>0.2240240424871445</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001722368528135121</v>
+        <v>0.00175489904358983</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.002191589446738362</v>
+        <v>0.04854431003332138</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.001209810376167297</v>
+        <v>0.03057635948061943</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002063750522211194</v>
+        <v>0.1427597999572754</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0005958873662166297</v>
+        <v>0.0255020447075367</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0009564731735736132</v>
+        <v>0.04401834309101105</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001278920797631145</v>
+        <v>0.02151616662740707</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0003403036389499903</v>
+        <v>0.1230602264404297</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.004906836431473494</v>
+        <v>0.02870657294988632</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0009478268912062049</v>
+        <v>0.01731490343809128</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.003448547329753637</v>
+        <v>0.1013097912073135</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0002460292016621679</v>
+        <v>0.1669580042362213</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.004572618752717972</v>
+        <v>0.1193239465355873</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.004593057557940483</v>
+        <v>0.2031168937683105</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.004118506330996752</v>
+        <v>0.1921284198760986</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.003252745838835835</v>
+        <v>0.06611417233943939</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.001241650665178895</v>
+        <v>0.008498396724462509</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0009277422213926911</v>
+        <v>0.1016479954123497</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001938875997439027</v>
+        <v>0.02419854328036308</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.00149674853309989</v>
+        <v>0.07273348420858383</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002546704490669072</v>
+        <v>0.1075164526700974</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001359917456284165</v>
+        <v>0.03189674392342567</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001473454060032964</v>
+        <v>0.1671338379383087</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.939379429444671e-06</v>
+        <v>0.1616933643817902</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.418037133291364e-05</v>
+        <v>0.04219361394643784</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002564716851338744</v>
+        <v>0.07850245386362076</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.002069824142381549</v>
+        <v>0.1125612258911133</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001277626492083073</v>
+        <v>0.08101034909486771</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.000898169819265604</v>
+        <v>0.09597251564264297</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.002380906837061048</v>
+        <v>0.01027181930840015</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002391581947449595</v>
+        <v>0.1201657950878143</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0001484882668592036</v>
+        <v>0.1113966852426529</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001790326932677999</v>
+        <v>0.04386970400810242</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001445231377147138</v>
+        <v>0.05038093402981758</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.001288805855438113</v>
+        <v>0.02706684917211533</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0007123591494746506</v>
+        <v>0.01695646345615387</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0007834436255507171</v>
+        <v>0.1027300134301186</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0002379178768023849</v>
+        <v>0.06376650929450989</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.001384350587613881</v>
+        <v>0.07687003165483475</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0003356315428391099</v>
+        <v>0.04641339555382729</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.002536652842536569</v>
+        <v>0.01939013600349426</v>
       </c>
       <c r="EM8" t="n">
-        <v>8.209038060158491e-05</v>
+        <v>0.0006718174554407597</v>
       </c>
       <c r="EN8" t="n">
-        <v>1.629001053515822e-05</v>
+        <v>0.009580373764038086</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002030514180660248</v>
+        <v>0.01140253990888596</v>
       </c>
       <c r="EP8" t="n">
-        <v>4.842528142035007e-06</v>
+        <v>0.06627151370048523</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.001565837068483233</v>
+        <v>0.02748783677816391</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.001346639590337873</v>
+        <v>0.1086099147796631</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003033873159438372</v>
+        <v>0.08212805539369583</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.002238815883174539</v>
+        <v>0.00302081648260355</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.001575341913849115</v>
+        <v>0.0674113929271698</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0003827043692581356</v>
+        <v>0.01765882968902588</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001435752841643989</v>
+        <v>0.01388606429100037</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0006226437399163842</v>
+        <v>0.03791767358779907</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.002111193258315325</v>
+        <v>0.2549271285533905</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001046058256179094</v>
+        <v>0.00439885538071394</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0009956620633602142</v>
+        <v>0.04319650679826736</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.001724090427160263</v>
+        <v>0.003508612047880888</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.001753998454660177</v>
+        <v>0.1403550207614899</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0014778837794438</v>
+        <v>0.0909726694226265</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0003315997018944472</v>
+        <v>0.06037158519029617</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.00200947979465127</v>
+        <v>0.03675106912851334</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0004858048632740974</v>
+        <v>0.03693606704473495</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.001339459209702909</v>
+        <v>0.2619963586330414</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.000820051645860076</v>
+        <v>0.04264824092388153</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.002259325701743364</v>
+        <v>0.1906859874725342</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.002053595148026943</v>
+        <v>0.06751248240470886</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.002599543426185846</v>
+        <v>0.1553502231836319</v>
       </c>
       <c r="FM8" t="n">
-        <v>4.827597877010703e-05</v>
+        <v>0.1809917688369751</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.001206575077958405</v>
+        <v>0.3113247752189636</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001916646375320852</v>
+        <v>0.03826836869120598</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001237524440512061</v>
+        <v>0.1566643118858337</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.003034185152500868</v>
+        <v>0.4482987523078918</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.001123552909120917</v>
+        <v>0.0291367694735527</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.003782397601753473</v>
+        <v>0.1898971647024155</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.004459818359464407</v>
+        <v>0.07613427191972733</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.003554272465407848</v>
+        <v>0.2691887617111206</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0002802064409479499</v>
+        <v>0.1626028418540955</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.002400768687948585</v>
+        <v>0.02182054333388805</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0003662593371700495</v>
+        <v>0.1092367395758629</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.003246515057981014</v>
+        <v>0.08952783048152924</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.002427658997476101</v>
+        <v>0.1102529987692833</v>
       </c>
       <c r="GA8" t="n">
-        <v>8.40634384076111e-05</v>
+        <v>0.03219721466302872</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.001498291501775384</v>
+        <v>0.1153394877910614</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0008059790125116706</v>
+        <v>0.009792390279471874</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.001524839783087373</v>
+        <v>0.001939376350492239</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.00230840896256268</v>
+        <v>0.06250180304050446</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.002045596484094858</v>
+        <v>0.1161401569843292</v>
       </c>
       <c r="GG8" t="n">
-        <v>5.991473153699189e-05</v>
+        <v>0.09004949778318405</v>
       </c>
     </row>
     <row r="9">
@@ -5551,3416 +5551,5692 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.02270948886871338</v>
+        <v>6.199289055075496e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9598749279975891</v>
+        <v>6.746055078110658e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03515980392694473</v>
+        <v>8.082591375568882e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1475381553173065</v>
+        <v>4.735491529572755e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3837268650531769</v>
+        <v>0.0001586860162205994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05684642493724823</v>
+        <v>5.910634172323626e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1640302389860153</v>
+        <v>0.0001409979886375368</v>
       </c>
       <c r="H10" t="n">
-        <v>1.020108580589294</v>
+        <v>0.0001687817275524139</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1975321769714355</v>
+        <v>4.304448520997539e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1849512159824371</v>
+        <v>0.0002165133773814887</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7733005881309509</v>
+        <v>3.023017416126095e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05647082254290581</v>
+        <v>2.822630267473869e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1244154870510101</v>
+        <v>8.761913341004401e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4299974143505096</v>
+        <v>0.0002782584342639893</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06593189388513565</v>
+        <v>4.313535100664012e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3878931105136871</v>
+        <v>0.0003781740088015795</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8369911313056946</v>
+        <v>0.0003088486555498093</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3420904576778412</v>
+        <v>0.0001217202661791816</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03544044494628906</v>
+        <v>0.0001445335801690817</v>
       </c>
       <c r="T10" t="n">
-        <v>0.179777979850769</v>
+        <v>0.0001487814442953095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07083681225776672</v>
+        <v>6.074579141568393e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1285934299230576</v>
+        <v>0.0001311858359258622</v>
       </c>
       <c r="W10" t="n">
-        <v>0.09809964895248413</v>
+        <v>0.0001231553615070879</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1473461985588074</v>
+        <v>6.04282395215705e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08019004017114639</v>
+        <v>2.936557393695693e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2802591919898987</v>
+        <v>0.0001915239699883386</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04387232288718224</v>
+        <v>5.549527850234881e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.07354668527841568</v>
+        <v>9.217419574270025e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1364253312349319</v>
+        <v>3.815162926912308e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001469871029257774</v>
+        <v>8.5902662249282e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.05261471122503281</v>
+        <v>0.0001079155772458762</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.06574079394340515</v>
+        <v>0.0001167571172118187</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1168385595083237</v>
+        <v>9.78835960268043e-05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.120245173573494</v>
+        <v>7.201608241302893e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1132497265934944</v>
+        <v>9.916079579852521e-05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.004287754185497761</v>
+        <v>2.406421845080331e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1245549321174622</v>
+        <v>0.0001557854702696204</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02321851253509521</v>
+        <v>0.0001284055178985</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01922171376645565</v>
+        <v>4.457187242223881e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.04385223984718323</v>
+        <v>4.002726564067416e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01538658980280161</v>
+        <v>1.265364699065685e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.07660840451717377</v>
+        <v>4.394512143335305e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.09307172149419785</v>
+        <v>7.977158929861616e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.04176535084843636</v>
+        <v>5.41321533091832e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.08724839240312576</v>
+        <v>4.191232437733561e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.1233034282922745</v>
+        <v>0.0002536352549213916</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4419004321098328</v>
+        <v>0.0004230766789987683</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.03481870517134666</v>
+        <v>7.804715278325602e-05</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.03482936695218086</v>
+        <v>0.0001010178093565628</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1394295394420624</v>
+        <v>2.975544521177653e-05</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.3394386470317841</v>
+        <v>3.441399894654751e-05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1376006305217743</v>
+        <v>5.636567948386073e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4109427034854889</v>
+        <v>0.0001165599096566439</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1719902455806732</v>
+        <v>0.0001050636274158023</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.02478122711181641</v>
+        <v>2.236647742392961e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.162708044052124</v>
+        <v>0.0003156432940158993</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.2617668211460114</v>
+        <v>8.909656025934964e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.002892866730690002</v>
+        <v>8.375450852327049e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.4066384136676788</v>
+        <v>0.000343459949363023</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.3970519602298737</v>
+        <v>8.613491809228435e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.01943391561508179</v>
+        <v>0.000184585020178929</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.4258221983909607</v>
+        <v>1.084828909370117e-05</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.2465695291757584</v>
+        <v>1.120166416512802e-06</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.02024968340992928</v>
+        <v>7.069227649481036e-06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1309394091367722</v>
+        <v>0.0002236188011011109</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.08049360662698746</v>
+        <v>4.043940862175077e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2936612367630005</v>
+        <v>7.151639147195965e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1550585180521011</v>
+        <v>0.0002132541121682152</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.07424331456422806</v>
+        <v>0.0002453841152600944</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.1235400885343552</v>
+        <v>2.158338247681968e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.002262390218675137</v>
+        <v>8.828499994706362e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.07171476632356644</v>
+        <v>2.711817614908796e-06</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.03420897200703621</v>
+        <v>0.0002274861035402864</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2983100116252899</v>
+        <v>0.0003131501143798232</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.1633870750665665</v>
+        <v>4.745326441479847e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01424002647399902</v>
+        <v>0.0001087833807105199</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2143862694501877</v>
+        <v>8.236735448008403e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1600974947214127</v>
+        <v>3.350740007590503e-05</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.1744347512722015</v>
+        <v>6.290966121014208e-05</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.2513633668422699</v>
+        <v>0.0001613807253306732</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.1170642450451851</v>
+        <v>1.131952012656257e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.07466983795166016</v>
+        <v>8.706095104571432e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2192925363779068</v>
+        <v>2.15878062590491e-05</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0941612720489502</v>
+        <v>2.318233600817621e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01140712015330791</v>
+        <v>7.624691352248192e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.05599137768149376</v>
+        <v>6.355466757668182e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.121612474322319</v>
+        <v>1.546171188238077e-05</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0305430069565773</v>
+        <v>4.27875311288517e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2166773527860641</v>
+        <v>4.468292172532529e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.04865626618266106</v>
+        <v>4.226582677802071e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.2565557658672333</v>
+        <v>6.638973718509078e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.03240877017378807</v>
+        <v>0.0002079851838061586</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.08809494972229004</v>
+        <v>1.163430079031968e-05</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.09288185089826584</v>
+        <v>7.655048830201849e-05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.2106685936450958</v>
+        <v>0.0002356012264499441</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02946687489748001</v>
+        <v>7.179217209341004e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.2179173827171326</v>
+        <v>0.0001800465397536755</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1307788342237473</v>
+        <v>7.317629206227139e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.05153639987111092</v>
+        <v>0.000145934012834914</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.05907387286424637</v>
+        <v>6.269298319239169e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1981004476547241</v>
+        <v>6.945456334506162e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.1226889193058014</v>
+        <v>2.420307100692298e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.08419468253850937</v>
+        <v>7.358017319347709e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03600537404417992</v>
+        <v>5.152327867108397e-05</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.07140400260686874</v>
+        <v>2.963447514048312e-07</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0410606637597084</v>
+        <v>4.796900975634344e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1731511354446411</v>
+        <v>8.103276923066005e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01130611728876829</v>
+        <v>5.023527410230599e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07581019401550293</v>
+        <v>9.88988031167537e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.2790190279483795</v>
+        <v>1.918160523928236e-05</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.05161173641681671</v>
+        <v>2.094929732265882e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1955747902393341</v>
+        <v>0.0001014528897940181</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1158964261412621</v>
+        <v>0.0002143162419088185</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02788867242634296</v>
+        <v>0.0001780840684659779</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.06494966149330139</v>
+        <v>8.471597539028153e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.192993551492691</v>
+        <v>0.0001174995049950667</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.08308427780866623</v>
+        <v>0.0003880717558786273</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.03171378374099731</v>
+        <v>0.000202017545234412</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.09190205484628677</v>
+        <v>6.700517587887589e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.1879561841487885</v>
+        <v>1.255108145414852e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.03533051162958145</v>
+        <v>9.96414601104334e-05</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03081808425486088</v>
+        <v>5.346367106540129e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.04588279500603676</v>
+        <v>0.0002353011950617656</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.05959419906139374</v>
+        <v>2.408662112429738e-05</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1557058393955231</v>
+        <v>0.0001217238896060735</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.2216825485229492</v>
+        <v>9.162234164250549e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.02325520291924477</v>
+        <v>4.644585715141147e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.2673520445823669</v>
+        <v>4.866637391387485e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.07759006321430206</v>
+        <v>3.493258918751962e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.1119481101632118</v>
+        <v>3.427778574405238e-05</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1395332515239716</v>
+        <v>0.0002185341581935063</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.1738634705543518</v>
+        <v>8.192253153538331e-05</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.04603952169418335</v>
+        <v>8.372549200430512e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.09580090641975403</v>
+        <v>5.915857764193788e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.09690559655427933</v>
+        <v>3.426082912483253e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.08294081687927246</v>
+        <v>2.3556607629871e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.1565741151571274</v>
+        <v>5.008577863918617e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.06022578477859497</v>
+        <v>9.069177031051368e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0486687645316124</v>
+        <v>1.938845161930658e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01971947774291039</v>
+        <v>2.682737613213249e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.006020628847181797</v>
+        <v>3.614981687860563e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.03817581757903099</v>
+        <v>9.879580466076732e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.210831955075264</v>
+        <v>5.248747766017914e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.08471762388944626</v>
+        <v>1.79402377398219e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.1471580862998962</v>
+        <v>1.631590203032829e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.04992283880710602</v>
+        <v>5.619454168481752e-05</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.1812683492898941</v>
+        <v>0.0001120994202210568</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.03570463135838509</v>
+        <v>5.256988879409619e-05</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.151991680264473</v>
+        <v>4.205886943964288e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1016977056860924</v>
+        <v>5.412263271864504e-05</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.1772696822881699</v>
+        <v>4.510094731813297e-05</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1190217509865761</v>
+        <v>0.0001068153724190779</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.08439583331346512</v>
+        <v>6.830808706581593e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.09660814702510834</v>
+        <v>8.842942770570517e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.2045346200466156</v>
+        <v>1.393887396261562e-05</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.09471972286701202</v>
+        <v>1.055532629834488e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03758989274501801</v>
+        <v>7.456557068508118e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.06926967203617096</v>
+        <v>3.411708894418553e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.08214705437421799</v>
+        <v>9.585909538145643e-06</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.08705250918865204</v>
+        <v>4.338280996307731e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.1907840669155121</v>
+        <v>9.418399713467807e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.03927366808056831</v>
+        <v>7.551599992439151e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.02562598697841167</v>
+        <v>3.826079773716629e-05</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02925347723066807</v>
+        <v>9.216128091793507e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.179018571972847</v>
+        <v>0.0001340196176897734</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0497981533408165</v>
+        <v>7.236946112243459e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.1663214415311813</v>
+        <v>7.559930963907391e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.07935788482427597</v>
+        <v>2.152930392185226e-05</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.04968469589948654</v>
+        <v>2.851071621989831e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.04602291062474251</v>
+        <v>3.017273775185458e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.09232282638549805</v>
+        <v>0.0001184446518891491</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.2472811788320541</v>
+        <v>0.0001228344335686415</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0342247448861599</v>
+        <v>0.0001402881316607818</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.1962436586618423</v>
+        <v>0.000417417730204761</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0639023557305336</v>
+        <v>0.0001104667462641373</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1522481590509415</v>
+        <v>0.0002967406762763858</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.1940442025661469</v>
+        <v>4.769227598444559e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.06410384178161621</v>
+        <v>1.709967000351753e-05</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.001486063934862614</v>
+        <v>1.526141204521991e-05</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.1661707907915115</v>
+        <v>0.0001883104559965432</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.3149081468582153</v>
+        <v>0.0001030460698530078</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02464226447045803</v>
+        <v>0.0001436262245988473</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.07349096983671188</v>
+        <v>2.15993459278252e-05</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.04421538487076759</v>
+        <v>0.0002041055704466999</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.05068729445338249</v>
+        <v>0.0001434359874110669</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.1435013860464096</v>
+        <v>1.828968379413709e-05</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.03874891996383667</v>
+        <v>6.652484444202855e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.004032874014228582</v>
+        <v>8.367780537810177e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1011359319090843</v>
+        <v>3.53790819644928e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.004733455367386341</v>
+        <v>0.6158401370048523</v>
       </c>
       <c r="B11" t="n">
-        <v>0.099366694688797</v>
+        <v>0.8775825500488281</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02047921158373356</v>
+        <v>0.4730165600776672</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07115519046783447</v>
+        <v>0.04934721440076828</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04089102521538734</v>
+        <v>0.2767888307571411</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02738094888627529</v>
+        <v>0.3548884391784668</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002582371234893799</v>
+        <v>0.1633719205856323</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002440603217110038</v>
+        <v>0.1346053779125214</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01516332477331161</v>
+        <v>0.0666193887591362</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01739238761365414</v>
+        <v>0.3776213228702545</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09225219488143921</v>
+        <v>1.244314670562744</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01668079383671284</v>
+        <v>0.3878063261508942</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07797861099243164</v>
+        <v>0.04488713294267654</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02032255381345749</v>
+        <v>0.2333250045776367</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01974722184240818</v>
+        <v>0.008086493238806725</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01457593310624361</v>
+        <v>0.2009640038013458</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01832126453518867</v>
+        <v>0.1542069613933563</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009699415415525436</v>
+        <v>0.09624028205871582</v>
       </c>
       <c r="S11" t="n">
-        <v>0.003759989980608225</v>
+        <v>0.06046510487794876</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01957122422754765</v>
+        <v>0.02497068420052528</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007511334493756294</v>
+        <v>0.196571946144104</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003156316466629505</v>
+        <v>0.06401687860488892</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02037530764937401</v>
+        <v>0.3177188336849213</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01305030658841133</v>
+        <v>0.165515810251236</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01370603963732719</v>
+        <v>0.00223727710545063</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0007364065386354923</v>
+        <v>0.03833092376589775</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.008904246613383293</v>
+        <v>0.1498680412769318</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01767635159194469</v>
+        <v>0.2876525819301605</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.008678789250552654</v>
+        <v>0.1899664402008057</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01660511270165443</v>
+        <v>0.3556761145591736</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0118718259036541</v>
+        <v>0.1681907325983047</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.003830624744296074</v>
+        <v>0.2447894513607025</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.433576345443726e-06</v>
+        <v>0.1040478348731995</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.009695060551166534</v>
+        <v>0.08283800631761551</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.003850434208288789</v>
+        <v>0.1176212877035141</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003218229860067368</v>
+        <v>0.1267780810594559</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.009498577564954758</v>
+        <v>0.02560258284211159</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01197020709514618</v>
+        <v>0.3856965899467468</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.006417184136807919</v>
+        <v>0.005626920610666275</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.007773006800562143</v>
+        <v>0.003503747284412384</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0002281868364661932</v>
+        <v>0.1311784982681274</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.006030275020748377</v>
+        <v>0.05014173686504364</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.001718796323984861</v>
+        <v>0.03260336816310883</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.004023203160613775</v>
+        <v>0.07238264381885529</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.002094843192026019</v>
+        <v>0.01302218623459339</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.01274801790714264</v>
+        <v>0.121671125292778</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.04621062427759171</v>
+        <v>0.4276797473430634</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0004053474403917789</v>
+        <v>0.126403346657753</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.02949183620512486</v>
+        <v>0.02232205867767334</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.007126795593649149</v>
+        <v>0.2364495545625687</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01327777747064829</v>
+        <v>0.08863601833581924</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.02450914308428764</v>
+        <v>0.07894469797611237</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.006206050515174866</v>
+        <v>0.1193249225616455</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0002197003923356533</v>
+        <v>0.05041952803730965</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.001084811519831419</v>
+        <v>0.7399467825889587</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02953252382576466</v>
+        <v>0.00674457848072052</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01904022321105003</v>
+        <v>0.4406834840774536</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.01058678701519966</v>
+        <v>0.002517275512218475</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.02833736874163151</v>
+        <v>0.4654673337936401</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.009821509011089802</v>
+        <v>0.03952119499444962</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.03659846261143684</v>
+        <v>0.03375617414712906</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.01653648726642132</v>
+        <v>0.2048849612474442</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02607764676213264</v>
+        <v>0.07575825601816177</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01857033558189869</v>
+        <v>0.1229300051927567</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01359735336154699</v>
+        <v>0.1482610106468201</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.007235871627926826</v>
+        <v>0.01657246984541416</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0005821785889565945</v>
+        <v>0.06251166760921478</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.007194554433226585</v>
+        <v>0.2407202273607254</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.006974607240408659</v>
+        <v>0.2732751667499542</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.007189153227955103</v>
+        <v>0.001068959012627602</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0003305424470454454</v>
+        <v>0.05156608298420906</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.002467869548127055</v>
+        <v>0.116763636469841</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.005049355328083038</v>
+        <v>0.1007027700543404</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.02158590219914913</v>
+        <v>0.437237948179245</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01538156531751156</v>
+        <v>0.1967731118202209</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.01944467052817345</v>
+        <v>0.09853626787662506</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0142105994746089</v>
+        <v>0.2940792143344879</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.01064753718674183</v>
+        <v>0.08624206483364105</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.01047923322767019</v>
+        <v>0.1544068157672882</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.004529885947704315</v>
+        <v>0.04602107778191566</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.002321534557268023</v>
+        <v>0.09577586501836777</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0004853730788454413</v>
+        <v>0.1320839822292328</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.01516069192439318</v>
+        <v>0.3628857731819153</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.003390064928680658</v>
+        <v>0.1822397708892822</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.00693940045312047</v>
+        <v>0.08924129605293274</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0003764844150282443</v>
+        <v>0.007066125050187111</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.001715894788503647</v>
+        <v>0.1204698756337166</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.004739562980830669</v>
+        <v>0.02350134775042534</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.004301207605749369</v>
+        <v>0.03164153918623924</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.002977430587634444</v>
+        <v>0.007984766736626625</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.016706183552742</v>
+        <v>0.06471721082925797</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.001265271101146936</v>
+        <v>0.4398202896118164</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0005847015418112278</v>
+        <v>0.1163652241230011</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.02009020745754242</v>
+        <v>0.08828818798065186</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.02812563441693783</v>
+        <v>0.1936606615781784</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02044475823640823</v>
+        <v>0.2989908754825592</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.002209325321018696</v>
+        <v>0.05244217067956924</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01903817988932133</v>
+        <v>0.006360307335853577</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.001369934994727373</v>
+        <v>0.08446791768074036</v>
       </c>
       <c r="CV11" t="n">
-        <v>8.886976866051555e-05</v>
+        <v>0.09631159156560898</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0163507703691721</v>
+        <v>0.3544855713844299</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.003329381579533219</v>
+        <v>0.1532865911722183</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01006475742906332</v>
+        <v>0.01558252051472664</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.001224766718223691</v>
+        <v>0.03310512006282806</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.003319872776046395</v>
+        <v>0.08267828077077866</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.006262556649744511</v>
+        <v>0.01603871956467628</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001142319990321994</v>
+        <v>0.03444066271185875</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.002624400891363621</v>
+        <v>0.03302521258592606</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01911801099777222</v>
+        <v>0.03230585157871246</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.006657151971012354</v>
+        <v>0.8809443116188049</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001100756810046732</v>
+        <v>0.2625964879989624</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.005090869963169098</v>
+        <v>0.1938831806182861</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.008744662627577782</v>
+        <v>0.1656044721603394</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01247111707925797</v>
+        <v>0.2949634492397308</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.01110885478556156</v>
+        <v>0.0377504825592041</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.002664706669747829</v>
+        <v>0.1515122056007385</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01083679404109716</v>
+        <v>0.001280620694160461</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0009312754264101386</v>
+        <v>0.07909131795167923</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.01374932564795017</v>
+        <v>0.1253154426813126</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.007668772246688604</v>
+        <v>0.06620380282402039</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0008451631292700768</v>
+        <v>0.1188861504197121</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01911714486777782</v>
+        <v>0.07903654873371124</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.00781644694507122</v>
+        <v>0.1171779632568359</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.000248549273237586</v>
+        <v>0.03537119179964066</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.003414930310100317</v>
+        <v>0.2020959258079529</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.004646464716643095</v>
+        <v>0.1529524475336075</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.001962273381650448</v>
+        <v>0.3020831942558289</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.014155981130898</v>
+        <v>0.5003432035446167</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.006128000095486641</v>
+        <v>0.2270054072141647</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.008473913185298443</v>
+        <v>0.03523041307926178</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0002811525482684374</v>
+        <v>0.1275071203708649</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.004048695787787437</v>
+        <v>0.1954046934843063</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.002698580035939813</v>
+        <v>0.01665493473410606</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001027568592689931</v>
+        <v>0.2919134497642517</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0116554219275713</v>
+        <v>0.09839940071105957</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.005024502985179424</v>
+        <v>0.1113395690917969</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0119908032938838</v>
+        <v>0.1667665392160416</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.002671535359695554</v>
+        <v>0.02310221642255783</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.01498314179480076</v>
+        <v>0.04866150394082069</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01881899870932102</v>
+        <v>0.06808348000049591</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.008695075288414955</v>
+        <v>0.1105386391282082</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01358798239380121</v>
+        <v>0.00367489829659462</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0003022107994183898</v>
+        <v>0.04521706700325012</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0006814564112573862</v>
+        <v>0.09095919132232666</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.002214828040450811</v>
+        <v>0.02316726371645927</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.008020535111427307</v>
+        <v>0.2384390532970428</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01087726559489965</v>
+        <v>0.09092027693986893</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.01039279904216528</v>
+        <v>0.1146837472915649</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.006481361575424671</v>
+        <v>0.1223313957452774</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01356495544314384</v>
+        <v>0.006470575928688049</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.01168653462082148</v>
+        <v>0.08603794872760773</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0002978160046041012</v>
+        <v>0.05673848837614059</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.00834950152784586</v>
+        <v>0.1568342000246048</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.002540581626817584</v>
+        <v>0.1187538206577301</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.01633650995790958</v>
+        <v>0.4259575605392456</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0007402595947496593</v>
+        <v>0.1609019190073013</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.009924156591296196</v>
+        <v>0.06410121917724609</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003562421072274446</v>
+        <v>0.07416896522045135</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.004287818446755409</v>
+        <v>0.08854670077562332</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.00654497416689992</v>
+        <v>0.01725886575877666</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0002197984140366316</v>
+        <v>0.03778063878417015</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.003504235530272126</v>
+        <v>0.06128029525279999</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.001280474243685603</v>
+        <v>0.03524254634976387</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0003681615926325321</v>
+        <v>0.03679248690605164</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.005627191159874201</v>
+        <v>0.1279090344905853</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01623188331723213</v>
+        <v>0.0243096686899662</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.006923890672624111</v>
+        <v>0.1565898358821869</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.005990206263959408</v>
+        <v>0.1032799035310745</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.003789446782320738</v>
+        <v>0.02441418543457985</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.008113236166536808</v>
+        <v>0.07492242753505707</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01808980293571949</v>
+        <v>0.08818314969539642</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.007044638507068157</v>
+        <v>0.2041937112808228</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.01543502882122993</v>
+        <v>0.2324856370687485</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.00586044741794467</v>
+        <v>0.1245941966772079</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02114456705749035</v>
+        <v>0.09575300663709641</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03510125353932381</v>
+        <v>0.6769686937332153</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0248849168419838</v>
+        <v>0.2909696102142334</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01696254126727581</v>
+        <v>0.1643003076314926</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.002767562866210938</v>
+        <v>0.02809503674507141</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0005927616730332375</v>
+        <v>0.2965439260005951</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01524704322218895</v>
+        <v>0.1343802064657211</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0006212845910340548</v>
+        <v>0.3547792732715607</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.00395388575270772</v>
+        <v>0.09263045340776443</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.003232474671676755</v>
+        <v>0.03915264457464218</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0001043505035340786</v>
+        <v>0.1280342489480972</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.003858733689412475</v>
+        <v>0.1309577822685242</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.004809701815247536</v>
+        <v>0.04033592343330383</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.006059281062334776</v>
+        <v>0.1507180333137512</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.006416046991944313</v>
+        <v>0.00925787165760994</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2250075340270996</v>
+        <v>0.368236631155014</v>
       </c>
       <c r="B12" t="n">
-        <v>2.212819337844849</v>
+        <v>0.6796796917915344</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3067339956760406</v>
+        <v>0.1957907676696777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5351195335388184</v>
+        <v>0.1591140925884247</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6980479955673218</v>
+        <v>0.4265561401844025</v>
       </c>
       <c r="F12" t="n">
-        <v>1.925527453422546</v>
+        <v>0.161849170923233</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3526948690414429</v>
+        <v>0.3752124011516571</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6062096357345581</v>
+        <v>0.5132041573524475</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2463716864585876</v>
+        <v>0.3727034032344818</v>
       </c>
       <c r="J12" t="n">
-        <v>0.447287380695343</v>
+        <v>0.422202080488205</v>
       </c>
       <c r="K12" t="n">
-        <v>1.751295328140259</v>
+        <v>0.9448423981666565</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3280973136425018</v>
+        <v>0.03679117560386658</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5760962963104248</v>
+        <v>0.2560318112373352</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132232278585434</v>
+        <v>0.3421705067157745</v>
       </c>
       <c r="O12" t="n">
-        <v>1.346688508987427</v>
+        <v>0.3484751582145691</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1439948230981827</v>
+        <v>0.5462905168533325</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3364956378936768</v>
+        <v>0.5098235607147217</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05925543606281281</v>
+        <v>0.04220224916934967</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02558723092079163</v>
+        <v>0.08012199401855469</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02092590369284153</v>
+        <v>0.1194732412695885</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1393758058547974</v>
+        <v>0.1487323343753815</v>
       </c>
       <c r="V12" t="n">
-        <v>0.285215824842453</v>
+        <v>0.02752392739057541</v>
       </c>
       <c r="W12" t="n">
-        <v>0.558684229850769</v>
+        <v>0.01345786638557911</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04108243063092232</v>
+        <v>0.1627262532711029</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.107645608484745</v>
+        <v>0.1315729469060898</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1372113674879074</v>
+        <v>0.06286439299583435</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.110462948679924</v>
+        <v>0.01289530657231808</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2300064414739609</v>
+        <v>0.2371399253606796</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2986480593681335</v>
+        <v>0.1024464443325996</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1184913516044617</v>
+        <v>0.4006621837615967</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.09830278903245926</v>
+        <v>0.09743793308734894</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2265172153711319</v>
+        <v>0.3481305837631226</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2470951974391937</v>
+        <v>0.1004291325807571</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07186558842658997</v>
+        <v>0.06173370778560638</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03728841990232468</v>
+        <v>0.01135869883000851</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.04360684752464294</v>
+        <v>0.02088911086320877</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.1767353266477585</v>
+        <v>0.1587045192718506</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.5176036953926086</v>
+        <v>0.6354308128356934</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.1260222345590591</v>
+        <v>0.02662887424230576</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.1418739408254623</v>
+        <v>0.04695872589945793</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.1772550344467163</v>
+        <v>0.2868873476982117</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.3965304791927338</v>
+        <v>0.1757551580667496</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.209298700094223</v>
+        <v>0.0773736760020256</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.1926354467868805</v>
+        <v>0.1079766973853111</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.3664794564247131</v>
+        <v>0.1698596924543381</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.2371464818716049</v>
+        <v>0.3904772400856018</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.225474119186401</v>
+        <v>1.055566787719727</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1437748074531555</v>
+        <v>0.2114867866039276</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2359921783208847</v>
+        <v>0.1847755163908005</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.300520122051239</v>
+        <v>0.03483286872506142</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.337507128715515</v>
+        <v>0.2020782828330994</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.5856896638870239</v>
+        <v>0.07693596184253693</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.07931223511695862</v>
+        <v>0.280339390039444</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.7625662088394165</v>
+        <v>0.0328529104590416</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.04232035577297211</v>
+        <v>0.07886600494384766</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1470369547605515</v>
+        <v>0.649212121963501</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.2707827389240265</v>
+        <v>0.03968194127082825</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.03240124136209488</v>
+        <v>0.01064929366111755</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.7402655482292175</v>
+        <v>0.4607165157794952</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.1902117282152176</v>
+        <v>0.07670954614877701</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.2009028643369675</v>
+        <v>0.1618088483810425</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.09281934052705765</v>
+        <v>0.2734887897968292</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4094643890857697</v>
+        <v>0.3104660212993622</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.02791249006986618</v>
+        <v>0.1082171648740768</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.2106622755527496</v>
+        <v>0.220181792974472</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0633048489689827</v>
+        <v>0.1453607380390167</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01386331114917994</v>
+        <v>0.1362039595842361</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.4885220229625702</v>
+        <v>0.2307036519050598</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.1830196976661682</v>
+        <v>0.2318643480539322</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.08888974785804749</v>
+        <v>0.2123288214206696</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.2272734045982361</v>
+        <v>0.06067728251218796</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.06598207354545593</v>
+        <v>0.1351902186870575</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08221056312322617</v>
+        <v>0.2010270953178406</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.7192239761352539</v>
+        <v>0.5669694542884827</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.1878044158220291</v>
+        <v>0.1225457042455673</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.2553796768188477</v>
+        <v>0.1699209213256836</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.3840154111385345</v>
+        <v>0.05659403651952744</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.5476200580596924</v>
+        <v>0.1692245751619339</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0407344289124012</v>
+        <v>0.02425466477870941</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.1207781881093979</v>
+        <v>0.1791870892047882</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.3083774745464325</v>
+        <v>0.06169966608285904</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.03807743266224861</v>
+        <v>0.08217881619930267</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.4246205687522888</v>
+        <v>0.2694471478462219</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.1269058585166931</v>
+        <v>0.01093688607215881</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.05279015749692917</v>
+        <v>0.087556391954422</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.03728309273719788</v>
+        <v>0.04538271203637123</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.308277815580368</v>
+        <v>0.0834973007440567</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.1416703015565872</v>
+        <v>0.04852471128106117</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.1165018528699875</v>
+        <v>0.06733621656894684</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.1325994729995728</v>
+        <v>0.1391774415969849</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.2300806641578674</v>
+        <v>0.1115819215774536</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.2601118683815002</v>
+        <v>0.3590613603591919</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.04182654619216919</v>
+        <v>0.2131192833185196</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.2750139534473419</v>
+        <v>0.05081931874155998</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1754892915487289</v>
+        <v>0.1462681591510773</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01081066951155663</v>
+        <v>0.1196551769971848</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.3097746968269348</v>
+        <v>0.3286985456943512</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.2305572926998138</v>
+        <v>0.0826120600104332</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.3434845209121704</v>
+        <v>0.1633632779121399</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.09199769049882889</v>
+        <v>0.05530653521418571</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.465314120054245</v>
+        <v>0.2840512096881866</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.1056720018386841</v>
+        <v>0.004213348031044006</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1417784541845322</v>
+        <v>0.0722341388463974</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.1035782545804977</v>
+        <v>0.0698162317276001</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.350520133972168</v>
+        <v>0.07724624127149582</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.1047016829252243</v>
+        <v>0.06438092142343521</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.2504600882530212</v>
+        <v>0.07525047659873962</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.08960352092981339</v>
+        <v>0.1522490680217743</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1501625180244446</v>
+        <v>0.1686142385005951</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.2381726652383804</v>
+        <v>0.2897854745388031</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.02717674523591995</v>
+        <v>0.3972659707069397</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0337938666343689</v>
+        <v>0.05156000331044197</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.4544345438480377</v>
+        <v>0.2205764651298523</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.5289774537086487</v>
+        <v>0.2945625185966492</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.3032988011837006</v>
+        <v>0.1340438574552536</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.7256758213043213</v>
+        <v>0.1538683474063873</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.2656286358833313</v>
+        <v>0.05026835203170776</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.1361140161752701</v>
+        <v>0.1475223004817963</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01911178976297379</v>
+        <v>0.05528686195611954</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.02286660298705101</v>
+        <v>0.1386659145355225</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.1779595762491226</v>
+        <v>0.2405633330345154</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.1518578082323074</v>
+        <v>0.05008415877819061</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1397148072719574</v>
+        <v>0.2671895623207092</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.3867156505584717</v>
+        <v>0.1750183403491974</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.1032340377569199</v>
+        <v>0.1373318284749985</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.2155336290597916</v>
+        <v>0.2973801493644714</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.04903120547533035</v>
+        <v>0.03867357224225998</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01445331424474716</v>
+        <v>0.1642799079418182</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.008028224110603333</v>
+        <v>0.1182104647159576</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.04853367805480957</v>
+        <v>0.1969365924596786</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.3062425851821899</v>
+        <v>0.1160058155655861</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.04421699047088623</v>
+        <v>0.3440724313259125</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.05517923459410667</v>
+        <v>0.01225132867693901</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.001978836953639984</v>
+        <v>0.142309159040451</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.2172601222991943</v>
+        <v>0.003330016508698463</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.1544315069913864</v>
+        <v>0.0136433020234108</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.2400262653827667</v>
+        <v>0.3294936418533325</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.1638000160455704</v>
+        <v>0.02161158993840218</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.3881109952926636</v>
+        <v>0.07319895923137665</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1049111410975456</v>
+        <v>0.05366187170147896</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.003519259393215179</v>
+        <v>0.04820789396762848</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.2262593507766724</v>
+        <v>0.07534602284431458</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.03034622967243195</v>
+        <v>0.02329794690012932</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.02436383441090584</v>
+        <v>0.1113091707229614</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01830488443374634</v>
+        <v>0.1852708160877228</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.3847776651382446</v>
+        <v>0.1878357231616974</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.02410571277141571</v>
+        <v>0.1231785714626312</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.08832800388336182</v>
+        <v>0.2510008811950684</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.1560651808977127</v>
+        <v>0.1021195203065872</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.5663675665855408</v>
+        <v>0.09175550192594528</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.4229585230350494</v>
+        <v>0.09998162835836411</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.4980857074260712</v>
+        <v>0.1410423964262009</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.1204016357660294</v>
+        <v>0.01222135312855244</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.107235960662365</v>
+        <v>0.04453545063734055</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.4230119287967682</v>
+        <v>0.3018249273300171</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.01877793297171593</v>
+        <v>0.04160809144377708</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.03804418444633484</v>
+        <v>0.0460437573492527</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.1409375965595245</v>
+        <v>0.01392476446926594</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.2306327372789383</v>
+        <v>0.04545524716377258</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.238885760307312</v>
+        <v>0.02834623865783215</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.2009094655513763</v>
+        <v>0.08125597238540649</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.1620492041110992</v>
+        <v>0.1635055840015411</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.05311967432498932</v>
+        <v>0.2540967166423798</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.4193059206008911</v>
+        <v>0.1377583146095276</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.1025389656424522</v>
+        <v>0.2548330128192902</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1979285180568695</v>
+        <v>0.111462414264679</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.2614194750785828</v>
+        <v>0.2127898931503296</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.03419733047485352</v>
+        <v>0.05340328812599182</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.1077720001339912</v>
+        <v>0.06953269988298416</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.1873889267444611</v>
+        <v>0.2551674842834473</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.1621847748756409</v>
+        <v>0.5791816115379333</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.1086003556847572</v>
+        <v>0.09499572962522507</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.7115408182144165</v>
+        <v>0.5445224642753601</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.1585671454668045</v>
+        <v>0.4525655508041382</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.1606269925832748</v>
+        <v>0.4361082315444946</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.3389767706394196</v>
+        <v>0.09221059828996658</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.4385079443454742</v>
+        <v>0.5514203906059265</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.2067030668258667</v>
+        <v>0.241622120141983</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.1597080528736115</v>
+        <v>0.2400090098381042</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.05658643692731857</v>
+        <v>0.01120105013251305</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.5479125380516052</v>
+        <v>0.1082634925842285</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.09654732793569565</v>
+        <v>0.3178174495697021</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.2227200865745544</v>
+        <v>0.2062883526086807</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.1509738266468048</v>
+        <v>0.04813283681869507</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.322295427322388</v>
+        <v>0.2873277068138123</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.2581692934036255</v>
+        <v>0.06612284481525421</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.6304746866226196</v>
+        <v>0.05381006002426147</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.3449569940567017</v>
+        <v>0.1905685365200043</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0906374529004097</v>
+        <v>0.01982469297945499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02725626900792122</v>
+        <v>0.1769389510154724</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0953180268406868</v>
+        <v>0.4678297638893127</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0117743406444788</v>
+        <v>0.07062804698944092</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03635993599891663</v>
+        <v>0.4863209128379822</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1560934484004974</v>
+        <v>0.8186746835708618</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07747586816549301</v>
+        <v>1.123552203178406</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05272427201271057</v>
+        <v>0.3667064309120178</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03282619640231133</v>
+        <v>0.2484616339206696</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03808432817459106</v>
+        <v>0.160230964422226</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03569503128528595</v>
+        <v>0.1175298988819122</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1022526025772095</v>
+        <v>1.089182138442993</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05390588194131851</v>
+        <v>0.1254969835281372</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1241711229085922</v>
+        <v>0.2081986218690872</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07001873105764389</v>
+        <v>0.9285469055175781</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06289277225732803</v>
+        <v>1.187227368354797</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01698256470263004</v>
+        <v>0.4761674404144287</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04247633367776871</v>
+        <v>0.3497179746627808</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0862223356962204</v>
+        <v>0.1720882058143616</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03643707185983658</v>
+        <v>0.09451096504926682</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06888314336538315</v>
+        <v>0.03946379572153091</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06926683336496353</v>
+        <v>0.004195023328065872</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06610400974750519</v>
+        <v>0.5254502892494202</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06372853368520737</v>
+        <v>0.4573992490768433</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06946346908807755</v>
+        <v>0.2330485433340073</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04903700202703476</v>
+        <v>0.09687525033950806</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.006071882322430611</v>
+        <v>0.1070358976721764</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02580316737294197</v>
+        <v>0.29961758852005</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02366004325449467</v>
+        <v>0.009132989682257175</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1335371434688568</v>
+        <v>0.1391518861055374</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.009112436324357986</v>
+        <v>0.2928781509399414</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.08430482447147369</v>
+        <v>0.07873302698135376</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.005046481266617775</v>
+        <v>0.2529613971710205</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01694480702280998</v>
+        <v>0.3706203401088715</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01232107356190681</v>
+        <v>0.2047035098075867</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.05305067077279091</v>
+        <v>0.697940468788147</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.00336279533803463</v>
+        <v>0.1189288944005966</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01267049834132195</v>
+        <v>0.05110779777169228</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01664485596120358</v>
+        <v>0.1574189960956573</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.005496875382959843</v>
+        <v>0.09735147655010223</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.03471750393509865</v>
+        <v>0.3287693858146667</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.003844285383820534</v>
+        <v>0.1039824411273003</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.05240463092923164</v>
+        <v>0.1177087351679802</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01349745038896799</v>
+        <v>0.1412784159183502</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01387004181742668</v>
+        <v>0.1561561822891235</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.01367361098527908</v>
+        <v>0.1165989711880684</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.02417536079883575</v>
+        <v>0.1545425653457642</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.07624875009059906</v>
+        <v>1.600207924842834</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04525798559188843</v>
+        <v>0.07060040533542633</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.02164019644260406</v>
+        <v>0.1643746048212051</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1380867809057236</v>
+        <v>0.3908764123916626</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0346103198826313</v>
+        <v>0.48903489112854</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02610671333968639</v>
+        <v>0.09700503945350647</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02697624266147614</v>
+        <v>0.2322589755058289</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.03956957533955574</v>
+        <v>0.1552767306566238</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.01558620482683182</v>
+        <v>0.3187461197376251</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04742656275629997</v>
+        <v>0.6639009714126587</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.02367333881556988</v>
+        <v>0.3213081359863281</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.01189133338630199</v>
+        <v>0.4726437926292419</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01297700311988592</v>
+        <v>0.7209758162498474</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.03041808307170868</v>
+        <v>0.005937651731073856</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01510530523955822</v>
+        <v>0.03272020816802979</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01832237839698792</v>
+        <v>0.1781465709209442</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.02544424310326576</v>
+        <v>0.210084468126297</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01003841683268547</v>
+        <v>0.04173924028873444</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01469695381820202</v>
+        <v>0.7123568654060364</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.02718230150640011</v>
+        <v>0.02952535636723042</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.07168175280094147</v>
+        <v>0.09284044802188873</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1023185029625893</v>
+        <v>0.6697449088096619</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.005369091406464577</v>
+        <v>0.6037092804908752</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.01224814727902412</v>
+        <v>0.7353962063789368</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.07908421754837036</v>
+        <v>0.2178605645895004</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.01948759146034718</v>
+        <v>0.05746299028396606</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.04991342127323151</v>
+        <v>0.1358975023031235</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05739601701498032</v>
+        <v>0.8870408535003662</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01747929304838181</v>
+        <v>0.02155640721321106</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.01399082690477371</v>
+        <v>0.4513152837753296</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.05970189347863197</v>
+        <v>0.2617103159427643</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.03260451182723045</v>
+        <v>0.2626400291919708</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01411847025156021</v>
+        <v>0.05266989767551422</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.04887647926807404</v>
+        <v>0.09401543438434601</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.02925861813127995</v>
+        <v>0.3575665056705475</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.005219859071075916</v>
+        <v>0.006196856498718262</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.03060194104909897</v>
+        <v>0.3258709013462067</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01473307609558105</v>
+        <v>0.05175352096557617</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0176728367805481</v>
+        <v>0.1205377876758575</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.00347820483148098</v>
+        <v>0.0916665717959404</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.006334127858281136</v>
+        <v>0.2801292538642883</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0004795435816049576</v>
+        <v>0.2151882946491241</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0151557307690382</v>
+        <v>0.04290366917848587</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01559439674019814</v>
+        <v>0.02836540900170803</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02621082216501236</v>
+        <v>0.2967541217803955</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.005540978629142046</v>
+        <v>0.8510147333145142</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.04798324778676033</v>
+        <v>0.3802416324615479</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.05321048945188522</v>
+        <v>0.2170361131429672</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.04689886420965195</v>
+        <v>0.1845015436410904</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.06378595530986786</v>
+        <v>0.3450842499732971</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.04089671745896339</v>
+        <v>0.3611693978309631</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.07389528304338455</v>
+        <v>0.2374732345342636</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.007213068660348654</v>
+        <v>0.01778224110603333</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0008559427224099636</v>
+        <v>0.1005343049764633</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0517321303486824</v>
+        <v>0.2489710003137589</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.02454014122486115</v>
+        <v>0.06312835216522217</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02581799030303955</v>
+        <v>0.0341096967458725</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.007516937796026468</v>
+        <v>0.1206589639186859</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02415634319186211</v>
+        <v>0.2575820088386536</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.002408801577985287</v>
+        <v>0.09134544432163239</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.009970702230930328</v>
+        <v>0.06583661586046219</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.00829135999083519</v>
+        <v>0.02615529671311378</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0112944059073925</v>
+        <v>0.4409987330436707</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.05470355600118637</v>
+        <v>0.09980334341526031</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.02295112423598766</v>
+        <v>0.04182159155607224</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1333553493022919</v>
+        <v>0.1914190500974655</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06518518179655075</v>
+        <v>0.1611054837703705</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.05237622931599617</v>
+        <v>0.03620732575654984</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.07748766988515854</v>
+        <v>0.2360469698905945</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.04760581254959106</v>
+        <v>0.642354428768158</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.07274166494607925</v>
+        <v>0.2668106555938721</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.06001457199454308</v>
+        <v>0.1705879718065262</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.009280135855078697</v>
+        <v>0.07261417061090469</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01489288359880447</v>
+        <v>0.06492027640342712</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.02527621947228909</v>
+        <v>0.4176002442836761</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03043801337480545</v>
+        <v>0.3345622420310974</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.02266915142536163</v>
+        <v>0.1097641289234161</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0205994900316</v>
+        <v>0.07749949395656586</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.03997258096933365</v>
+        <v>0.2218394577503204</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.01697675883769989</v>
+        <v>0.007982820272445679</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.03345231339335442</v>
+        <v>0.05387936905026436</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.07993081212043762</v>
+        <v>0.3236007690429688</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02680106647312641</v>
+        <v>0.2480549812316895</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.04567335173487663</v>
+        <v>0.02202233672142029</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.06858489662408829</v>
+        <v>0.3559470474720001</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.02286607585847378</v>
+        <v>0.5161109566688538</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.008496789261698723</v>
+        <v>0.1610385328531265</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.06162764504551888</v>
+        <v>0.1190862283110619</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.006344927474856377</v>
+        <v>0.06969563663005829</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.1137785315513611</v>
+        <v>0.02704040706157684</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.004064914304763079</v>
+        <v>0.2142482548952103</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.003141008317470551</v>
+        <v>0.1381637156009674</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.005231374409049749</v>
+        <v>0.1435994952917099</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.009561936371028423</v>
+        <v>0.04807243496179581</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0368676595389843</v>
+        <v>0.3428150117397308</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.001324324868619442</v>
+        <v>0.01937412098050117</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.002632159274071455</v>
+        <v>0.07869454473257065</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.04004316404461861</v>
+        <v>0.06522849202156067</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001592136453837156</v>
+        <v>0.1003773361444473</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.00102305831387639</v>
+        <v>0.2626842260360718</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.05330459401011467</v>
+        <v>0.2006603330373764</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.05829440057277679</v>
+        <v>0.1119102239608765</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.03985023126006126</v>
+        <v>0.09089954197406769</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0167949590831995</v>
+        <v>0.0154451048001647</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.02544216997921467</v>
+        <v>0.1762363463640213</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.009325329214334488</v>
+        <v>0.3676663935184479</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.007896887138485909</v>
+        <v>0.2594013512134552</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002066120505332947</v>
+        <v>0.04761401563882828</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.04804414138197899</v>
+        <v>0.3716989755630493</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.02894224599003792</v>
+        <v>0.07398827373981476</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.005326574668288231</v>
+        <v>0.0450427234172821</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02743195742368698</v>
+        <v>0.09415889531373978</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.005555774550884962</v>
+        <v>0.3074012696743011</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.002649518195539713</v>
+        <v>0.2343612611293793</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.02031164430081844</v>
+        <v>0.04874435067176819</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01508805342018604</v>
+        <v>0.09152080863714218</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.006853576749563217</v>
+        <v>0.1651044189929962</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01324369385838509</v>
+        <v>0.2756885290145874</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.01074867323040962</v>
+        <v>0.09891755878925323</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01715628057718277</v>
+        <v>0.4422624409198761</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.09415806829929352</v>
+        <v>0.3554014265537262</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01148230582475662</v>
+        <v>0.1254692673683167</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.00743386521935463</v>
+        <v>0.05965862050652504</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.01759690418839455</v>
+        <v>0.5524047017097473</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.02233604714274406</v>
+        <v>0.08508691191673279</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.03983572125434875</v>
+        <v>0.2758120000362396</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.1154926344752312</v>
+        <v>0.07896481454372406</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01787782274186611</v>
+        <v>0.125872939825058</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.1272033154964447</v>
+        <v>0.1446910798549652</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.05748725682497025</v>
+        <v>0.329185962677002</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.03628908842802048</v>
+        <v>0.3661232590675354</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.04066313430666924</v>
+        <v>0.1243007257580757</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.02044003270566463</v>
+        <v>0.5195207595825195</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.05492785945534706</v>
+        <v>0.1312806904315948</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.003582416102290154</v>
+        <v>0.09382666647434235</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.03542649745941162</v>
+        <v>0.1652741134166718</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.02457848377525806</v>
+        <v>0.1460340917110443</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.05441140383481979</v>
+        <v>0.07537972927093506</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.1225462108850479</v>
+        <v>0.2453674077987671</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.07921876758337021</v>
+        <v>0.3701337873935699</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.04520658776164055</v>
+        <v>0.04573294520378113</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.02269333973526955</v>
+        <v>0.2017474919557571</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.02327535673975945</v>
+        <v>0.1823307126760483</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.399875367904315e-07</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>1.07799871784664e-06</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.16436731648173e-07</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.994927055828157e-07</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.955698962774477e-07</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.820897864490689e-06</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.341845117825869e-07</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.784483386785723e-07</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.143456351826444e-08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.969502759242459e-07</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>7.799657169016427e-07</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3.957743786031642e-07</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.642841927055997e-08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.534385205559374e-07</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53577559558471e-06</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.372819238871671e-07</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.339440013405692e-07</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.462298027694487e-07</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.941111236192228e-07</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.119356423690988e-08</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.701018561561796e-07</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>3.614869967805134e-07</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.406435951092135e-07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.09058975744847e-07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.863604250564094e-08</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.541067575772104e-07</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.61090666653763e-08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.129386858650832e-09</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.167075112107341e-07</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.502971400668685e-07</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.470750004590627e-08</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>7.081800390551507e-08</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.148398305569572e-08</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.661451917329032e-08</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.959028553410462e-08</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.136568030801755e-07</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.136142143172037e-07</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.659807224996257e-08</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.244377625032939e-09</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.370016431996191e-07</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.040887719407692e-08</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.079676448829559e-07</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.197559527099656e-07</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.511460064004496e-08</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.070007430025726e-08</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.185337835835526e-08</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.532794039529108e-07</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.663841472549393e-08</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.489039670512284e-07</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.107255798160622e-08</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.053862661137828e-06</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.798065625280287e-07</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.650380904218764e-07</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.293074043625893e-08</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.916722507961822e-07</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.279844579788914e-07</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.17937027255266e-07</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.040965452782984e-07</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.321166215959238e-07</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.098480476637633e-07</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.564212581683933e-08</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2.626549466810957e-08</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.67855276345108e-07</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.946297700783362e-08</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.220140231656842e-07</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>3.048865551136259e-07</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.892911155072397e-08</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>7.219783526579704e-08</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.58867061120327e-08</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>4.540532927421737e-08</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.440778659884018e-08</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.696437537812017e-08</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.263254603145469e-07</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.172061416809811e-07</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.032359335795263e-07</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>1.252871868473449e-07</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.062815696035614e-08</v>
+        <v>0</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.831844305248524e-07</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.537357049614002e-08</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>1.864139989038449e-07</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.576286194904242e-07</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.393749281599412e-08</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.787777108575028e-07</v>
+        <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.621863697844674e-08</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.850913816132561e-08</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.166268148722338e-07</v>
+        <v>0</v>
       </c>
       <c r="CI14" t="n">
-        <v>3.297411979019671e-07</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>9.477152929093791e-08</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>2.471969935413654e-07</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>9.857693328285677e-09</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>9.912260878763846e-08</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.963184329018986e-07</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>9.597793848570291e-08</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>8.434385989630755e-08</v>
+        <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.502319489394722e-07</v>
+        <v>0</v>
       </c>
       <c r="CR14" t="n">
-        <v>2.18101057214426e-08</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>8.320728994704041e-08</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.218138289184935e-08</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>2.977974133955286e-07</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>4.892145710755358e-08</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.369836439835126e-07</v>
+        <v>0</v>
       </c>
       <c r="CX14" t="n">
-        <v>2.098235540870519e-08</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.490194456721383e-08</v>
+        <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.687968875785373e-08</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.379651616342016e-07</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.053114075943995e-07</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.484619301412749e-07</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.434344731876536e-08</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>3.781675843583798e-07</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>6.523269746594451e-08</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>8.520462557726205e-09</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>4.772599027091928e-07</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>3.945223170376266e-07</v>
+        <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.207099356610343e-07</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.796442437144833e-09</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>4.914024316349241e-07</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>1.974225654066686e-07</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.96066366697778e-07</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>5.199595420890546e-09</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>8.711867849342525e-08</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.238875809889578e-08</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>1.867180117187672e-07</v>
+        <v>0</v>
       </c>
       <c r="DS14" t="n">
-        <v>2.71583019184618e-07</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
-        <v>2.028270529308429e-07</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>2.954734767968148e-08</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>1.020112989635891e-07</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>1.356493442017381e-07</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>2.252712789641009e-07</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.971093106742046e-08</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.186252032743141e-07</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>3.916967017403294e-08</v>
+        <v>0</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.863371264538728e-07</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.237091140637858e-07</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>4.087262084340182e-09</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>2.597923867142526e-07</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>2.356370316647372e-07</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>2.502537199688959e-07</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>1.257506738738812e-07</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>1.995014429212461e-07</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>3.565548212236536e-08</v>
+        <v>0</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.044657776423264e-07</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>1.341472142257771e-07</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>7.122945788751167e-08</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>7.528369927456424e-09</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>1.194396190840052e-07</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>1.574300796391981e-07</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>1.698944629424659e-07</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>1.711345589683333e-07</v>
+        <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>3.475839704947248e-08</v>
+        <v>0</v>
       </c>
       <c r="ET14" t="n">
-        <v>1.399647260313941e-07</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>8.510103555181558e-08</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>4.186990736343432e-07</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>3.481285659745481e-07</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>9.067777284599288e-08</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>1.299092957651737e-07</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>7.662850265433008e-08</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>3.673364190603934e-08</v>
+        <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>1.047331465997559e-07</v>
+        <v>0</v>
       </c>
       <c r="FC14" t="n">
-        <v>3.072876779697253e-07</v>
+        <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>7.645333255368314e-08</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>1.87974706022942e-07</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>6.154444065487041e-09</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>5.02581940509117e-08</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>2.372018883534111e-07</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>9.103283815647956e-08</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>4.423306450007658e-07</v>
+        <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>7.066066132210835e-08</v>
+        <v>0</v>
       </c>
       <c r="FL14" t="n">
-        <v>2.260269411635818e-07</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>1.488552356931905e-07</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>1.896668067047358e-08</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>6.964356202843192e-08</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>3.422381382733874e-07</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>2.589673613329069e-07</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>6.236451355334793e-09</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>8.974402732064846e-08</v>
+        <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>3.326558726257645e-07</v>
+        <v>0</v>
       </c>
       <c r="FU14" t="n">
-        <v>4.634840706785326e-07</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>1.45896905223708e-07</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>2.167958541576809e-07</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>1.977679602305216e-07</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>1.304040040395194e-07</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>1.089012897637076e-07</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>8.306950860514917e-08</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>2.176918343366196e-07</v>
+        <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>4.091875211997831e-07</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>1.524417712062132e-07</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>1.004044563046591e-07</v>
+        <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>3.176486629286046e-08</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>2.185390144404664e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>0.2879581451416016</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.5662530660629272</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.3113006949424744</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3197948932647705</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.460787832736969</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.1870093941688538</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2687153518199921</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.08498641848564148</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.1058431640267372</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.1418257504701614</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.7803014516830444</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.2800849676132202</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.3077804148197174</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.4448177516460419</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.05716554820537567</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.2456543743610382</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.08594360202550888</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.02781856618821621</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.0228397361934185</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1766789853572845</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1323418617248535</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1904026120901108</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1068247258663177</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.07106374949216843</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.03659701719880104</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.02743109874427319</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.1157213002443314</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.05884436145424843</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.001099934801459312</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>0.2665319740772247</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.06982407718896866</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.2087151706218719</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.09633435308933258</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>0.07548783719539642</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>0.2624175548553467</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.07468121498823166</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>0.0813857689499855</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>0.3688814342021942</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>4.176422953605652e-05</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>0.02968396618962288</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>0.3563170433044434</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>0.08008617907762527</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.0228903628885746</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>0.09056258201599121</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>0.06355993449687958</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>0.150643914937973</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>0.794564425945282</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.06687264889478683</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.2334302812814713</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>0.1788317561149597</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>0.0980796217918396</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.06557976454496384</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>0.1529656648635864</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>0.03390460461378098</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>0.2099144756793976</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>0.4071300625801086</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>0.3588230013847351</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>0.04027938097715378</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>0.8733702301979065</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>0.07341073453426361</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>0.05553124845027924</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>0.055592130869627</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>0.04486700147390366</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>0.1403816044330597</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>0.08092009276151657</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>0.04736956581473351</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>0.1520712226629257</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>0.09679017961025238</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>0.08136275410652161</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>0.1221329122781754</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>0.08339762687683105</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>0.08102138340473175</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>0.1560858488082886</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>0.6081879138946533</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>0.09914105385541916</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>0.1287036389112473</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>0.1077798679471016</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>0.09739596396684647</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>0.1445138901472092</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>0.01819607615470886</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>0.0594162717461586</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>0.1489350646734238</v>
       </c>
       <c r="CE15" t="n">
-        <v>0</v>
+        <v>0.2658684849739075</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>0.07517148554325104</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>0.1308376044034958</v>
       </c>
       <c r="CH15" t="n">
-        <v>0</v>
+        <v>0.07211413234472275</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>0.03429430350661278</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>0.01385393738746643</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>0.01957742497324944</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>0.02278745360672474</v>
       </c>
       <c r="CM15" t="n">
-        <v>0</v>
+        <v>0.1304810494184494</v>
       </c>
       <c r="CN15" t="n">
-        <v>0</v>
+        <v>0.3199936151504517</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>0.1157578900456429</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>0.1956906616687775</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0</v>
+        <v>0.3176392018795013</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>0.1557295471429825</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>0.1422758251428604</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>0.03924572095274925</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>0.01698961481451988</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>0.09080822765827179</v>
       </c>
       <c r="CW15" t="n">
-        <v>0</v>
+        <v>0.2193441092967987</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>0.07780303806066513</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>0.07379686832427979</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0</v>
+        <v>0.05415038764476776</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>0.04722479730844498</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>0.009543742053210735</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>0.04871264100074768</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>0.06418837606906891</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>0.1154365092515945</v>
       </c>
       <c r="DF15" t="n">
-        <v>0</v>
+        <v>0.1260617226362228</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>0.006726082414388657</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>0.1031783074140549</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.0258105956017971</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>0.1569077968597412</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>0.1567169427871704</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>0.2652465403079987</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>0.1389449387788773</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>0.1100078374147415</v>
       </c>
       <c r="DO15" t="n">
-        <v>0</v>
+        <v>0.0738433301448822</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>0.113760769367218</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>0.04410924017429352</v>
       </c>
       <c r="DR15" t="n">
-        <v>0</v>
+        <v>0.18787482380867</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>0.12789386510849</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>0.02851742878556252</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>0.1044579073786736</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>0.0308176688849926</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.1422794759273529</v>
       </c>
       <c r="DX15" t="n">
-        <v>0</v>
+        <v>0.3477921187877655</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>0.1538058668375015</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>0.104478694498539</v>
       </c>
       <c r="EA15" t="n">
-        <v>0</v>
+        <v>0.2864047884941101</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>0.09734487533569336</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>0.02685454487800598</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>0.1408354192972183</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>0.110938161611557</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>0.01162630692124367</v>
       </c>
       <c r="EG15" t="n">
-        <v>0</v>
+        <v>0.05700243264436722</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>0.02352267503738403</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>0.08877483755350113</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0</v>
+        <v>0.0275689885020256</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>0.06969564408063889</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>0.007600083015859127</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>0.07530917972326279</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>0.05676648020744324</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>0.07296030223369598</v>
       </c>
       <c r="EP15" t="n">
-        <v>0</v>
+        <v>0.1949155628681183</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>0.08168055862188339</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>0.02551625669002533</v>
       </c>
       <c r="ES15" t="n">
-        <v>0</v>
+        <v>0.09229832142591476</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>0.0148308239877224</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>0.02770336344838142</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>0.07974299788475037</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>0.004989056847989559</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>0.1528851240873337</v>
       </c>
       <c r="EY15" t="n">
-        <v>0</v>
+        <v>0.2617075741291046</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>0.07057782262563705</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>0.09120333194732666</v>
       </c>
       <c r="FB15" t="n">
-        <v>0</v>
+        <v>0.05472820252180099</v>
       </c>
       <c r="FC15" t="n">
-        <v>0</v>
+        <v>0.06099823117256165</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>0.02912269718945026</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>0.03788464143872261</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>0.05498264729976654</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>0.01249397918581963</v>
       </c>
       <c r="FH15" t="n">
-        <v>0</v>
+        <v>0.04890190437436104</v>
       </c>
       <c r="FI15" t="n">
-        <v>0</v>
+        <v>0.2033904492855072</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0</v>
+        <v>0.06535215675830841</v>
       </c>
       <c r="FK15" t="n">
-        <v>0</v>
+        <v>0.2838234603404999</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>0.1682501584291458</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>0.02610501088202</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>0.1162878349423409</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>0.1335546970367432</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>0.2344187200069427</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0</v>
+        <v>0.1166510656476021</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>0.0755082368850708</v>
       </c>
       <c r="FS15" t="n">
-        <v>0</v>
+        <v>0.04452411830425262</v>
       </c>
       <c r="FT15" t="n">
-        <v>0</v>
+        <v>0.3895850777626038</v>
       </c>
       <c r="FU15" t="n">
-        <v>0</v>
+        <v>0.2766894102096558</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>0.02381446957588196</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>0.05775558948516846</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>0.006410654634237289</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>0.1053366661071777</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0</v>
+        <v>0.1694891452789307</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>0.08089741319417953</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>0.02489827387034893</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>0.009338818490505219</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>0.07155415415763855</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>0.02979066409170628</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>0.06762535870075226</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>0.03347172960639</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.06315962225198746</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.2287777066230774</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.02990382350981236</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0610908716917038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2095146030187607</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.06904743611812592</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.04506457597017288</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.008457930758595467</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.04936112090945244</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.009261418133974075</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.3621420860290527</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.06937728822231293</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1260477155447006</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2829759120941162</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.02428642846643925</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0002626525238156319</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1195333749055862</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.07209578156471252</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01994532719254494</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.04985681176185608</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.0448913685977459</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.05462890118360519</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.05088042095303535</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.01394186355173588</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.01515738479793072</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.01368945185095072</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.009675963781774044</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.0241280235350132</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.01243265625089407</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.0300377644598484</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.02536708861589432</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.09438227862119675</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.02394548058509827</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.00931329932063818</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.04504499584436417</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.0009426283650100231</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.01425900682806969</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.08957425504922867</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.004699782002717257</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.0605420358479023</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.008197175338864326</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.02098372578620911</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.0307466946542263</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.06954776495695114</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.00690281530842185</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.05462944507598877</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.368866890668869</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.04545954614877701</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.01128641981631517</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.02396804094314575</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.01280557829886675</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.02417314797639847</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.02429444342851639</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.01312377024441957</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.1136379614472389</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.07899321615695953</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.02215364947915077</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.04794073104858398</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.1846384257078171</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.05317655205726624</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.002620676532387733</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.01372266188263893</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.03202950581908226</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02218190021812916</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.1301662176847458</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.02708216942846775</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.006453620735555887</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.1435908526182175</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.06593283265829086</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.09164545685052872</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.03273416683077812</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.02910828217864037</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.1167417615652084</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.2537773251533508</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.04703563451766968</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0.04986410588026047</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0.03345294669270515</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0.01983566954731941</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.05531913414597511</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0.02258346974849701</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.01584126614034176</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.01548210717737675</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.1009714752435684</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.01564638316631317</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.03891961276531219</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.05403636768460274</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.03405878692865372</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.01739835366606712</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.008321718312799931</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0.01444902643561363</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.08832012116909027</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0.2749009728431702</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.03323439508676529</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.136303573846817</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.01906801573932171</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0.002018895000219345</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0.01196172367781401</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0.02303275652229786</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0.009098459966480732</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0.01014523487538099</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0.08556482195854187</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0.0152091896161437</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.05363455414772034</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.02823209390044212</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0.0275394469499588</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0.004581454675644636</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0.005428413394838572</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0.01294436492025852</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.03706802427768707</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0.02518678642809391</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.008461007848381996</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0.02660415694117546</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.09779464453458786</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0.03641213476657867</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0.01290811505168676</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.00497879134491086</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0.0304292906075716</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.01097768638283014</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0.04169036448001862</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0.01115951966494322</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0.06276392191648483</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.03549674153327942</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.01489970274269581</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.01941715367138386</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0.05177490785717964</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0.007451278623193502</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.07417367398738861</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.03067203238606453</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0.01925487443804741</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0.00965571217238903</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0.006555436179041862</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0.02296610176563263</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0.04953020438551903</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0.08093763142824173</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0.01785715855658054</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0.03080401197075844</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0.001714713871479034</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0.004482918418943882</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0.0249797273427248</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.02492632530629635</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0.06412355601787567</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0.004105418920516968</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0.02211420610547066</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0.006718365009874105</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0.005408678203821182</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0.07516323029994965</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0.0168539360165596</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0.05094106122851372</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0.01421691663563251</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0.005892784800380468</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0.02528992295265198</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0.005368800368160009</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0.01448660064488649</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0.008685062639415264</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0.1080505549907684</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.01964887604117393</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.04227378219366074</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.03606439009308815</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0.02554373256862164</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0.0181923620402813</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0.005795528646558523</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0.01634716987609863</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0.04595741257071495</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.09832950681447983</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0.009389922022819519</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.1264420598745346</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.01673140004277229</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0.01436652056872845</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0.03119192644953728</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0.006441873498260975</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.030342947691679</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0.07532636076211929</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0.070929154753685</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.009889985434710979</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0.08821418136358261</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.1201711893081665</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0.04143273830413818</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0.09854469448328018</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0.05311369895935059</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.004108577035367489</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0.007872783578932285</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0.01793923601508141</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.01684227213263512</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.03949524089694023</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0.0291166715323925</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0.0008703856728971004</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0.01773138158023357</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0.05150951072573662</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0.02601661719381809</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.9991554021835327</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.420053005218506</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4737808704376221</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7808082699775696</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9038101434707642</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.117986440658569</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.02487111650407314</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1193298548460007</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.486946314573288</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5281398296356201</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.3348388671875</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4988771677017212</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9406052827835083</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.46381139755249</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8126043677330017</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5527997016906738</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8969376087188721</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.7402747273445129</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3531417548656464</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3017542362213135</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.02123390883207321</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1554819643497467</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.2045232206583023</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2647992670536041</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.02376078069210052</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.03564045950770378</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.02356264740228653</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1769434213638306</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.2889332175254822</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.2604787945747375</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.5284651517868042</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.2060075700283051</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.03930969908833504</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.272626519203186</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0449877455830574</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.1972477734088898</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1915721893310547</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.2932407259941101</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.04966853559017181</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.03052173554897308</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.05756266415119171</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.3312292098999023</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.2002647668123245</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.225755363702774</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.05574281513690948</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.01586350798606873</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.033088088035583</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.4663130342960358</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.394595205783844</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.7593697905540466</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.1059578508138657</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.03978551179170609</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.3046580851078033</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.02604812756180763</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.212892651557922</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.399085134267807</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.6987886428833008</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.07454762607812881</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.3402844369411469</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0.4079635441303253</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.2302432656288147</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.2650408148765564</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.2359799146652222</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.02968646585941315</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.3078276515007019</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.1466352939605713</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.3978160917758942</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.651523232460022</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0.581087052822113</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.0224508959800005</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.002953336574137211</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0.1713068783283234</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.5843541026115417</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1.303574800491333</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0.2590137422084808</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0.04994715005159378</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0.1975829303264618</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0.0564725287258625</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.2985713481903076</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0.3482665419578552</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.1891951262950897</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.20276939868927</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.3308653235435486</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.2638416886329651</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.01527723297476768</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.230220839381218</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.3361051976680756</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.1318355053663254</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.003459744155406952</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.1425608098506927</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.1074830889701843</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>1.079785823822021</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0.04619202762842178</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.5638018846511841</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.3853250741958618</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.5465840101242065</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0.2230477631092072</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0.656497597694397</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0.04904904589056969</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0.1085154265165329</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0.3874863386154175</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0.2214387655258179</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0.1603892147541046</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.1003270745277405</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.2613899707794189</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0.1175556629896164</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0.005388811230659485</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0.1320222467184067</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.1861171871423721</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1.720696210861206</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0.2481199651956558</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.544022798538208</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.1637594103813171</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.056875079870224</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0.05902861803770065</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0.01861412450671196</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0.1042739748954773</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.4077357053756714</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0.4188149273395538</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0.3508161306381226</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0.4839438796043396</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0.2856999635696411</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.2085460722446442</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.07690564543008804</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0.0485515184700489</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0.01166525855660439</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.4338374435901642</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0.3646650314331055</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0.3512231409549713</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0.3742002546787262</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0.01376377046108246</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.2758191227912903</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0.3617268204689026</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0.0390402190387249</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0.3296574056148529</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0.1011756509542465</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0.01574516296386719</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0.1793150454759598</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0.1102227121591568</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.07120807468891144</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.604139506816864</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0.132380336523056</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0.02008750289678574</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0.08380316942930222</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0.3881471157073975</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>0.1623350828886032</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0.4263159036636353</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0.2296936959028244</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>0.3615310788154602</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0.126616895198822</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0.07729391008615494</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0.1302998960018158</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0.1223449632525444</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0.1712559312582016</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0.512441873550415</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0.1870573759078979</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0.06749677658081055</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.1106181591749191</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.2720995843410492</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0.06598986685276031</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0.02106493338942528</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0.2101247757673264</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0.1663820445537567</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.3583432734012604</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0.1010549664497375</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0.1220217496156693</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>1.002757787704468</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0.1528720557689667</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0.2250756770372391</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0.07421319186687469</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0.2504284977912903</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0.156900629401207</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.4697076082229614</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0.3467936515808105</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0.02186455577611923</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>2.113073110580444</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0.4565269947052002</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0.254693865776062</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0.1584596037864685</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0.2227159440517426</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0.2347619384527206</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0.5969488620758057</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0.1688380837440491</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0.5996990203857422</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0.1989759206771851</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.2638146877288818</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0.2846270203590393</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0.008468421176075935</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0.314481794834137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.1144648790359497</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.06443402916193008</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.09096942096948624</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01882332190871239</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1067065000534058</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05699945241212845</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01883384957909584</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.06063134223222733</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.03543690964579582</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1698215305805206</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.07483135163784027</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0854441300034523</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.02823464386165142</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2438006401062012</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.03438234329223633</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.08595295250415802</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.05250182375311852</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1937451362609863</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.03203247487545013</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.01973084546625614</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.0577692985534668</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.009078990668058395</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.02022800967097282</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.02359170094132423</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.01533473376184702</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.1142197698354721</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.002026204951107502</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.04318168759346008</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.008922028355300426</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.007540364284068346</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.08579640090465546</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.03037979826331139</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.02662656828761101</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.08838954567909241</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.06122562289237976</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.03521553426980972</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.00992097333073616</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.05051953345537186</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.009924562647938728</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.03771322220563889</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.01775752380490303</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.01153191737830639</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.01792538166046143</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.04694299399852753</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.02385981380939484</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.140186682343483</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.07063876092433929</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.04417507350444794</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.0211591012775898</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.04004495590925217</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.07999347150325775</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.04567540809512138</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.01423053722828627</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.04214470088481903</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.1234691366553307</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.03819276764988899</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.01498373970389366</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.0185011588037014</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.06997957825660706</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.1070028841495514</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.01181634515523911</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.07739964127540588</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.01385622564703226</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.006381004117429256</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.01716399565339088</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.07369910925626755</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.06736092269420624</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.03158790990710258</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.004138839896768332</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.08070124685764313</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.07476280629634857</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.003454680787399411</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.07868252694606781</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.08613680303096771</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0.01545817404985428</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.1094716191291809</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.00912915263324976</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.003406411036849022</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.04560190439224243</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0.04360422492027283</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.05433125793933868</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.1034728512167931</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.03514464944601059</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.05986383184790611</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.01657045446336269</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.00540130166336894</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.01294202078133821</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.002438201103359461</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.001907611032947898</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0.01600490137934685</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.1372887939214706</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.1288156509399414</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0.006784480065107346</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0.03935278579592705</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>0.04647788777947426</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0.1075692921876907</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0.0229042824357748</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0.005975793115794659</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0.0550786480307579</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0.1013591140508652</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0.02138092741370201</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0.05202988162636757</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.02074183896183968</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0.008300192654132843</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0.004621462430804968</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0.006448738742619753</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0.007783306762576103</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0.02037562243640423</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0.1186577528715134</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.07212000340223312</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0.05448576807975769</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0.0127737894654274</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.08016940951347351</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0.1329436451196671</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0.07892435044050217</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.1082848235964775</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0.0677456259727478</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0.009958455339074135</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0.007243037223815918</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0.03485533595085144</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>0.05935949459671974</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>0.0477275662124157</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0.04171708971261978</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0.04554412513971329</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0.1597194224596024</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>0.0312244575470686</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0.0144360326230526</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>0.0003965478390455246</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>0.05658277124166489</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>0.01849257200956345</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>0.1167510002851486</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0.05799664556980133</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>0.137405201792717</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>0.05060796812176704</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>0.1074179708957672</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>0.09320826828479767</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0.04851563647389412</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>0.06560496240854263</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>0.01877309381961823</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>0.03271651640534401</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0.03720389306545258</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0.03235230594873428</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0.03064469434320927</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>0.0237758681178093</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>0.1326097548007965</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>0.02553144842386246</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>0.08160059154033661</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>0.00300995260477066</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>0.01124658342450857</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>0.04185610264539719</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>0.04870475456118584</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>0.06656048446893692</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>0.1463089138269424</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>0.1173439845442772</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>0.03325216472148895</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0.0437743104994297</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>0.03400910645723343</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>0.002673556562513113</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>0.0003654090687632561</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>0.00191778945736587</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>0.01580580696463585</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>0.02233855612576008</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>0.0464375913143158</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>0.09837313741445541</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>0.02067389339208603</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>0.09781905263662338</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>0.08763455599546432</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>0.03417253494262695</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>0.05397504568099976</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>0.08155034482479095</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>0.08468441665172577</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>0.09692540764808655</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>0.01118310447782278</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>0.03467018529772758</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>0.01480103842914104</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>0.07677607238292694</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>0.00167728029191494</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>0.000652410089969635</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>0.08507252484560013</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>0.07253153622150421</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>0.09486498683691025</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0.05680470168590546</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>0.004533883184194565</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>0.0829295814037323</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>0.01222986914217472</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>0.04380318894982338</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>0.06656897068023682</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>0.06772421300411224</v>
+      </c>
+      <c r="GG19" t="n">
+        <v>0.1352617591619492</v>
       </c>
     </row>
   </sheetData>
